--- a/Cobertura_IPERC_Administrativos_CAR.xlsx
+++ b/Cobertura_IPERC_Administrativos_CAR.xlsx
@@ -18,9 +18,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Alcance y criterios'!$A$4:$C$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Resumen por área'!$A$4:$I$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Matriz consolidada'!$A$4:$J$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Observaciones'!$A$4:$G$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Trazabilidad'!$A$4:$F$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Trazabilidad'!$A$4:$F$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -855,22 +855,22 @@
         <v>22</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>37</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -1086,22 +1086,22 @@
         <v>70</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F13" s="15" t="n">
         <v>101</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I13" s="14" t="inlineStr"/>
     </row>
@@ -2922,21 +2922,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-CI-D1</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Analista de Inventario</t>
+        </is>
+      </c>
       <c r="I44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -3786,21 +3790,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F64" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr"/>
-      <c r="H64" s="5" t="inlineStr"/>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-CI-D1</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Técnico de Inventario</t>
+        </is>
+      </c>
       <c r="I64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -4258,7 +4266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4373,20 +4381,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Operaciones</t>
+          <t>QSE &amp; Operational Excellence</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>TECNICO DE INVENTARIO</t>
+          <t>COORDINADOR DE EXCELENCIA OPERACIONAL</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>Professional</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -4396,7 +4404,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>4950 INVENTARY</t>
+          <t>4650 EXCELENCIA OPERACIONAL</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -4410,30 +4418,30 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>QSE &amp; Operational Excellence</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>COORDINADOR DE EXCELENCIA OPERACIONAL</t>
+          <t>CHOFER</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>BC Adm</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>4650 EXCELENCIA OPERACIONAL</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -4452,7 +4460,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>CHOFER</t>
+          <t>GERENTE GENERAL</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
@@ -4460,12 +4468,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>Top Management</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -4484,12 +4492,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>GERENTE GENERAL</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
@@ -4497,17 +4505,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Top Management</t>
+          <t>Professional</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
+          <t>5930 3ACM Expenses</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -4521,12 +4529,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>ANALISTA DE IMPUESTOS</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -4544,7 +4552,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>5930 3ACM Expenses</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -4563,7 +4571,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>ANALISTA DE IMPUESTOS</t>
+          <t>ANALISTA DE REDES</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
@@ -4581,7 +4589,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -4600,7 +4608,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>ANALISTA DE REDES</t>
+          <t>DIRECTOR FINANCIERO</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
@@ -4608,7 +4616,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>Top Management</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -4618,7 +4626,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -4637,7 +4645,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>DIRECTOR FINANCIERO</t>
+          <t>GERENTE FINANCIERO</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
@@ -4645,7 +4653,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Top Management</t>
+          <t>Middle Management</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -4674,7 +4682,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>GERENTE FINANCIERO</t>
+          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
@@ -4682,7 +4690,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Middle Management</t>
+          <t>Low Management</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -4692,7 +4700,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -4711,7 +4719,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
@@ -4719,7 +4727,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>Professional</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -4729,7 +4737,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -4748,7 +4756,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>MENSAJERO / REPARTIDOR</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -4756,7 +4764,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>BC Adm</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -4766,7 +4774,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -4785,7 +4793,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>MENSAJERO / REPARTIDOR</t>
+          <t>SENIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
@@ -4793,7 +4801,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>Professional</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -4803,7 +4811,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -4817,12 +4825,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>SENIOR BUSINESS CONTROLLER</t>
+          <t>APRENDIZ</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
@@ -4830,17 +4838,17 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>BC Adm</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
+          <t>3801 PLANTABAL MANTENANCE #1</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -4859,7 +4867,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>ANALISTA DE INVENTARIO</t>
+          <t>DIRECTOR DE OPERACIONES</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
@@ -4867,7 +4875,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>Top Management</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -4877,7 +4885,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>4950 INVENTARY</t>
+          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -4896,7 +4904,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>APRENDIZ</t>
+          <t>GERENTE DE PRODUCCION</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
@@ -4904,7 +4912,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>Middle Management</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -4914,7 +4922,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>3801 PLANTABAL MANTENANCE #1</t>
+          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -4933,7 +4941,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>DIRECTOR DE OPERACIONES</t>
+          <t>JEFE DE BODEGA</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
@@ -4941,7 +4949,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Top Management</t>
+          <t>Low Management</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -4951,7 +4959,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
+          <t>2500 SERVICE CENTER</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -4970,7 +4978,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>GERENTE DE PRODUCCION</t>
+          <t>JEFE DE PRODUCCION</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
@@ -4978,7 +4986,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Middle Management</t>
+          <t>Low Management</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -4999,82 +5007,8 @@
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Operaciones</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>JEFE DE BODEGA</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Low Management</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>2500 SERVICE CENTER</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Elaborar matriz IPERC para el puesto</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Operaciones</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>JEFE DE PRODUCCION</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Low Management</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Elaborar matriz IPERC para el puesto</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:I24"/>
+  <autoFilter ref="A4:I22"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -5608,7 +5542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5752,329 +5686,357 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-EHS-D1</t>
+          <t>GE-SO-CI-D1</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>EHS</t>
+          <t>Técnico de Inventario</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Ingeniero de seguridad y ambiente (13) · Tecnico de seguridad y ambiente (16)</t>
+          <t>Técnico de Inventario (14) · Analista de Inventario (10)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>a5c35af4-GE-SO-EHS-D1-_EHS.xlsx</t>
+          <t>7d905433-GE-SO-CI-D1_-_Control_de_Inventarios.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-EHS-D1</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Finanzas</t>
+          <t>EHS</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Coordinador Contable y de Impuestos (7) · Analista financiero (4) · Coordinador Contable (8) · Jefe de Contabilidad e Impuestos (9) · Coordinador de Tesoreria (6)</t>
+          <t>Ingeniero de seguridad y ambiente (13) · Tecnico de seguridad y ambiente (16)</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>109ebe9e-GE-SO-FI-D1_-_Finanzas.xlsx</t>
+          <t>a5c35af4-GE-SO-EHS-D1-_EHS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-IT-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Help Desk</t>
+          <t>Finanzas</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Help Desk (10) · Desarrollador JR (6) · Gerente tecnologico (6) · Analista de desarrollo y sistema (5)</t>
+          <t>Coordinador Contable y de Impuestos (7) · Analista financiero (4) · Coordinador Contable (8) · Jefe de Contabilidad e Impuestos (9) · Coordinador de Tesoreria (6)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>7794a690-GE-SO-IT-D1_-_IT.xlsx</t>
+          <t>109ebe9e-GE-SO-FI-D1_-_Finanzas.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-LE-D1</t>
+          <t>GE-SO-IT-D1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Help Desk</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Asistente Legal (11) · Analista Legal (10) · Coordinador/a de Asuntos Legales (10)</t>
+          <t>Help Desk (10) · Desarrollador JR (6) · Gerente tecnologico (6) · Analista de desarrollo y sistema (5)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>904e5c44-GE-SO-LE-D1_-_Legal.xlsx</t>
+          <t>7794a690-GE-SO-IT-D1_-_IT.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-LE-D1</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Mantenimiento - Administrativos</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>156</v>
+        <v>31</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Gerente JR de mantenimiento (20) · Jefe de mantenimiento (42) · Planificador de mantenimiento (21) · Supervisor de mantenimiento (38) · Auxiliar administrativo (35)</t>
+          <t>Asistente Legal (11) · Analista Legal (10) · Coordinador/a de Asuntos Legales (10)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>271a4bea-GE-SO-MA-D1_-_Mantenimiento.xlsx</t>
+          <t>904e5c44-GE-SO-LE-D1_-_Legal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PGS-D1</t>
+          <t>GE-SO-MA-D1</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Engicore</t>
+          <t>Mantenimiento - Administrativos</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Diseño e Ingenieria (9) · Ingeniero de Diseño e Ingenieria (14) · Analista de Diseño e Ingenieria (9)</t>
+          <t>Gerente JR de mantenimiento (20) · Jefe de mantenimiento (42) · Planificador de mantenimiento (21) · Supervisor de mantenimiento (38) · Auxiliar administrativo (35)</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>f4a8175b-GE-SO-PGS-D1_-_Engicore.xlsx</t>
+          <t>271a4bea-GE-SO-MA-D1_-_Mantenimiento.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1</t>
+          <t>GE-SO-PGS-D1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Planificación y Logística</t>
+          <t>Engicore</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Jefe de Planificación y Logística (11) · Coordinador de Supply Chain (6) · Programador de Producción (8) · Analista de Supply Chain (6)</t>
+          <t>Jefe de Diseño e Ingenieria (9) · Ingeniero de Diseño e Ingenieria (14) · Analista de Diseño e Ingenieria (9)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>1fa9982d-GE-SO-PO-D1_-_Planificaci_n_y_Log_stica.xlsx</t>
+          <t>f4a8175b-GE-SO-PGS-D1_-_Engicore.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PY-D1</t>
+          <t>GE-SO-PO-D1</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Proyectos</t>
+          <t>Planificación y Logística</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Proyectos (20) · Ingeniero de Proyectos (15) · Analista de Proyectos (16)</t>
+          <t>Jefe de Planificación y Logística (11) · Coordinador de Supply Chain (6) · Programador de Producción (8) · Analista de Supply Chain (6)</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>933cde5a-GE-SO-PY-D1_-_Proyectos.xlsx</t>
+          <t>1fa9982d-GE-SO-PO-D1_-_Planificaci_n_y_Log_stica.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SC-D1</t>
+          <t>GE-SO-PY-D1</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Compras</t>
+          <t>Proyectos</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
         <v>3</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Analista Supply Chain (13) · Analista Compras (14) · Jefe de Compras (13)</t>
+          <t>Jefe de Proyectos (20) · Ingeniero de Proyectos (15) · Analista de Proyectos (16)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>9c752964-GE-SO-SC-D1_-_Compras.xlsx</t>
+          <t>933cde5a-GE-SO-PY-D1_-_Proyectos.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Salud Ocupacional</t>
+          <t>Compras</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Medico Ocupacional (18) · Enfermero Ocupacional (10) · Auxiliar de servicios de salud (11)</t>
+          <t>Analista Supply Chain (13) · Analista Compras (14) · Jefe de Compras (13)</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>cf092d8f-GE-SO-SF-D1_-_Salud_ocupacional.xlsx</t>
+          <t>9c752964-GE-SO-SC-D1_-_Compras.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>RECURSOS HUMANOS</t>
+          <t>Salud Ocupacional</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>339</v>
+        <v>39</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>HR DIRECTOR AMERICAS (36) · HR BUSINNES PARTNER AMERICAS (42) · BUSINNES PARTNER DE RECURSOS HUMANOS (28) · COORDINADORA DE DESARROLLO ORGANIZACIONAL (49) · PEOPLE OPERATIONS PARTNER (42) · ANALISTA DE RECURSOS HUMANOS (72) · ANALISTA DE RECURSOS HUMANOS Y NÓMINA (28) · ANALISTA DE DESARROLLO ORGANIZACIONAL (42)</t>
+          <t>Medico Ocupacional (18) · Enfermero Ocupacional (10) · Auxiliar de servicios de salud (11)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>b206b7b5-GE-SO-TH-D1_-_RRHH.xlsx</t>
+          <t>cf092d8f-GE-SO-SF-D1_-_Salud_ocupacional.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>GE-SO-TH-D1</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>RECURSOS HUMANOS</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>339</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>HR DIRECTOR AMERICAS (36) · HR BUSINNES PARTNER AMERICAS (42) · BUSINNES PARTNER DE RECURSOS HUMANOS (28) · COORDINADORA DE DESARROLLO ORGANIZACIONAL (49) · PEOPLE OPERATIONS PARTNER (42) · ANALISTA DE RECURSOS HUMANOS (72) · ANALISTA DE RECURSOS HUMANOS Y NÓMINA (28) · ANALISTA DE DESARROLLO ORGANIZACIONAL (42)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>b206b7b5-GE-SO-TH-D1_-_RRHH.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>1083</v>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>1107</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F19"/>
+  <autoFilter ref="A4:F20"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/Cobertura_IPERC_Administrativos_CAR.xlsx
+++ b/Cobertura_IPERC_Administrativos_CAR.xlsx
@@ -564,7 +564,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Tratamiento CAR  ·  Verificación de cobertura IPERC - Personal administrativo</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Archivo 'HeadCount - V1.1', Hoja1 (base nominal, 817 registros). La Hoja2 contiene una tabla dinámica cuyos filtros fueron recuperados para replicar el criterio original.</t>
+          <t>Base nominal del head count del mes. La hoja se localiza automáticamente por sus encabezados; no se requiere tabla dinámica.</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Se excluye el área 'Silvicultura - Abastecimiento' (personal de campo). Confirmado por el responsable de la evaluación.</t>
+          <t>Se excluye el área 'Silvicultura - Abastecimiento' (personal de campo).</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Se excluyen las jerarquías 'BC Workers' y 'BC Leaders' (personal operativo). Se mantienen: BC Adm, Support Staff, Professional, Shift Supervisor, Low / Middle / Top Management.</t>
+          <t>Se excluyen las jerarquías 'BC Workers' y 'BC Leaders' (personal operativo).</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Se incluyen las localidades Quevedo y Samborondón. Se excluye Juárez (México).</t>
+          <t>Se incluyen las localidades Quevedo y Samborondón.</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Se excluye al personal con Localidad Principal 'High Point', por corresponder a colaboradores que no permanecen habitualmente en las instalaciones del país.</t>
+          <t>Se excluye al personal con Localidad Principal 'High Point'.</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Se mantienen dentro del alcance cargos como Supervisor de Producción, Supervisor de Mantenimiento, Chofer, Mensajero, Aprendiz, Jefe de Bodega, Técnico de Inventario, Enfermera/o y Médico Ocupacional.</t>
+          <t>Se mantienen dentro del alcance Supervisor de Producción, Supervisor de Mantenimiento, Chofer, Mensajero, Aprendiz, Jefe de Bodega, Técnico de Inventario, Enfermera/o y Médico Ocupacional.</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>El cruce se realiza por el par ÁREA + CARGO, no por el nombre del cargo de forma aislada, dado que existen cargos presentes en más de un área.</t>
+          <t>El cruce se realiza por el par ÁREA + CARGO, dado que existen cargos presentes en más de un área.</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Se neutralizan mayúsculas, tildes, dobles espacios, terminaciones de género y errores de tipeo. Las equivalencias no evidentes fueron validadas una a una con el responsable (ver hoja 5).</t>
+          <t>Se neutralizan mayúsculas, tildes, dobles espacios, terminaciones de género y errores de tipeo. Las equivalencias no evidentes están registradas en la hoja 5.</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Tratamiento CAR  ·  Verificación de cobertura IPERC - Personal administrativo</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Tratamiento CAR  ·  Verificación de cobertura IPERC - Personal administrativo</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Tratamiento CAR  ·  Verificación de cobertura IPERC - Personal administrativo</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Tratamiento CAR  ·  Verificación de cobertura IPERC - Personal administrativo</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Tratamiento CAR  ·  Verificación de cobertura IPERC - Personal administrativo</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 29/09/2026</t>
         </is>
       </c>
     </row>

--- a/Cobertura_IPERC_Administrativos_CAR.xlsx
+++ b/Cobertura_IPERC_Administrativos_CAR.xlsx
@@ -18,9 +18,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Alcance y criterios'!$A$4:$C$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Resumen por área'!$A$4:$I$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Matriz consolidada'!$A$4:$J$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$I$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Observaciones'!$A$4:$G$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Trazabilidad'!$A$4:$F$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Observaciones'!$A$4:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Trazabilidad'!$A$4:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -163,10 +163,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -564,7 +564,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 29/09/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 29/09/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -855,22 +855,22 @@
         <v>22</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>37</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -947,47 +947,47 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>QSE &amp; Operational Excellence</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>CON BRECHAS</t>
+        <v>0</v>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>ESG/Lab</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>0</v>
@@ -996,15 +996,15 @@
         <v>100</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
@@ -1013,14 +1013,14 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>ESG/Lab</t>
+          <t>Engicore</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>0</v>
@@ -1029,15 +1029,15 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
@@ -1046,14 +1046,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Engicore</t>
+          <t>QSE &amp; Operational Excellence</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>0</v>
@@ -1062,15 +1062,15 @@
         <v>100</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
@@ -1086,22 +1086,22 @@
         <v>70</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F13" s="15" t="n">
         <v>101</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I13" s="14" t="inlineStr"/>
     </row>
@@ -1146,7 +1146,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 29/09/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1270,7 +1270,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1314,7 +1314,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1358,7 +1358,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1402,7 +1402,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1446,23 +1446,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1 / GE-SO-SF-D1</t>
+          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo / Auxiliar de servicios de salud</t>
+          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1538,7 +1538,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1582,7 +1582,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1626,7 +1626,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1674,7 +1674,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1718,7 +1718,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1762,7 +1762,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1806,7 +1806,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1850,7 +1850,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1894,7 +1894,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1938,7 +1938,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1982,7 +1982,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2026,7 +2026,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2074,7 +2074,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2318,7 +2318,7 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2362,7 +2362,7 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2410,7 +2410,7 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2454,7 +2454,7 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2498,7 +2498,7 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2622,7 +2622,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2786,7 +2786,7 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2874,7 +2874,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F43" s="13" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2922,7 +2922,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2966,7 +2966,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F45" s="13" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3010,7 +3010,7 @@
           <t>Quevedo / Samborondon</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3098,23 +3098,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1 / GE-SO-SF-D1</t>
+          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo / Auxiliar de servicios de salud</t>
+          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
         </is>
       </c>
       <c r="I48" s="9" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3190,21 +3190,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr"/>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-RL-D35</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>Director de Operaciones</t>
+        </is>
+      </c>
       <c r="I50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -3230,21 +3234,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F51" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr"/>
-      <c r="H51" s="4" t="inlineStr"/>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-RL-D35</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Gerente de Producción</t>
+        </is>
+      </c>
       <c r="I51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -3270,7 +3278,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3314,7 +3322,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F53" s="13" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3398,7 +3406,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F55" s="13" t="inlineStr">
+      <c r="F55" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3446,7 +3454,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="F56" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3490,7 +3498,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F57" s="13" t="inlineStr">
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3574,7 +3582,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F59" s="13" t="inlineStr">
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3618,7 +3626,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr">
+      <c r="F60" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3662,7 +3670,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F61" s="13" t="inlineStr">
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3706,7 +3714,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F62" s="12" t="inlineStr">
+      <c r="F62" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3790,7 +3798,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F64" s="12" t="inlineStr">
+      <c r="F64" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3834,7 +3842,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F65" s="13" t="inlineStr">
+      <c r="F65" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3878,7 +3886,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F66" s="12" t="inlineStr">
+      <c r="F66" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3922,21 +3930,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F67" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr"/>
-      <c r="H67" s="4" t="inlineStr"/>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-EO-D1</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Coordinador de Excelencia Operacional</t>
+        </is>
+      </c>
       <c r="I67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -3962,7 +3974,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F68" s="12" t="inlineStr">
+      <c r="F68" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -4006,7 +4018,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F69" s="13" t="inlineStr">
+      <c r="F69" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -4050,7 +4062,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F70" s="12" t="inlineStr">
+      <c r="F70" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -4098,7 +4110,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F71" s="13" t="inlineStr">
+      <c r="F71" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -4142,7 +4154,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F72" s="12" t="inlineStr">
+      <c r="F72" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -4186,7 +4198,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F73" s="13" t="inlineStr">
+      <c r="F73" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -4230,7 +4242,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F74" s="12" t="inlineStr">
+      <c r="F74" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -4266,7 +4278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4290,7 +4302,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 29/09/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -4381,30 +4393,30 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>QSE &amp; Operational Excellence</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>COORDINADOR DE EXCELENCIA OPERACIONAL</t>
+          <t>CHOFER</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>BC Adm</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>4650 EXCELENCIA OPERACIONAL</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -4423,7 +4435,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>CHOFER</t>
+          <t>GERENTE GENERAL</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -4431,12 +4443,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>Top Management</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -4455,12 +4467,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>GERENTE GENERAL</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
@@ -4468,17 +4480,17 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Top Management</t>
+          <t>Professional</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
+          <t>5930 3ACM Expenses</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -4492,12 +4504,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>ANALISTA DE IMPUESTOS</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
@@ -4515,7 +4527,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>5930 3ACM Expenses</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -4534,7 +4546,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>ANALISTA DE IMPUESTOS</t>
+          <t>ANALISTA DE REDES</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -4552,7 +4564,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -4571,7 +4583,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>ANALISTA DE REDES</t>
+          <t>DIRECTOR FINANCIERO</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
@@ -4579,7 +4591,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>Top Management</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -4589,7 +4601,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -4608,7 +4620,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>DIRECTOR FINANCIERO</t>
+          <t>GERENTE FINANCIERO</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
@@ -4616,7 +4628,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Top Management</t>
+          <t>Middle Management</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -4645,7 +4657,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>GERENTE FINANCIERO</t>
+          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
@@ -4653,7 +4665,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Middle Management</t>
+          <t>Low Management</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -4663,7 +4675,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -4682,7 +4694,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
@@ -4690,7 +4702,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>Professional</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -4700,7 +4712,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -4719,7 +4731,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>MENSAJERO / REPARTIDOR</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
@@ -4727,7 +4739,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>BC Adm</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -4737,7 +4749,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -4756,7 +4768,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>MENSAJERO / REPARTIDOR</t>
+          <t>SENIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -4764,7 +4776,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>Professional</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -4774,7 +4786,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -4788,12 +4800,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>SENIOR BUSINESS CONTROLLER</t>
+          <t>APRENDIZ</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
@@ -4801,17 +4813,17 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>BC Adm</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
+          <t>3801 PLANTABAL MANTENANCE #1</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -4830,7 +4842,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>APRENDIZ</t>
+          <t>JEFE DE BODEGA</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
@@ -4838,7 +4850,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>Low Management</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -4848,7 +4860,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>3801 PLANTABAL MANTENANCE #1</t>
+          <t>2500 SERVICE CENTER</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -4867,7 +4879,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>DIRECTOR DE OPERACIONES</t>
+          <t>JEFE DE PRODUCCION</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
@@ -4875,7 +4887,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Top Management</t>
+          <t>Low Management</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -4896,119 +4908,8 @@
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Operaciones</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>GERENTE DE PRODUCCION</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Middle Management</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Elaborar matriz IPERC para el puesto</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Operaciones</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>JEFE DE BODEGA</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Low Management</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>2500 SERVICE CENTER</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Elaborar matriz IPERC para el puesto</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Operaciones</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>JEFE DE PRODUCCION</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Low Management</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Elaborar matriz IPERC para el puesto</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:I22"/>
+  <autoFilter ref="A4:I19"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -5023,7 +4924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5045,7 +4946,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 29/09/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -5526,8 +5427,41 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-RL-D35</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Jefe de Producción (MV y Secado)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>(no consta)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>SIN CLASIFICAR - detectado este mes</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Puesto evaluado en la matriz que no aparece en el head count del mes</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Definir si es cargo nuevo, denominación alterna o cargo suprimido</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G16"/>
+  <autoFilter ref="A4:G17"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -5542,7 +5476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5563,7 +5497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 29/09/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -5742,301 +5676,357 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-EO-D1</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Finanzas</t>
+          <t>Excelencia Operacional</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Coordinador Contable y de Impuestos (7) · Analista financiero (4) · Coordinador Contable (8) · Jefe de Contabilidad e Impuestos (9) · Coordinador de Tesoreria (6)</t>
+          <t>Coordinador de Excelencia Operacional (12)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>109ebe9e-GE-SO-FI-D1_-_Finanzas.xlsx</t>
+          <t>6e2db6dc-GE-SO-EO-D1_-_Excelencia_Operacional.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-IT-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Help Desk</t>
+          <t>Finanzas</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Help Desk (10) · Desarrollador JR (6) · Gerente tecnologico (6) · Analista de desarrollo y sistema (5)</t>
+          <t>Coordinador Contable y de Impuestos (7) · Analista financiero (4) · Coordinador Contable (8) · Jefe de Contabilidad e Impuestos (9) · Coordinador de Tesoreria (6)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>7794a690-GE-SO-IT-D1_-_IT.xlsx</t>
+          <t>109ebe9e-GE-SO-FI-D1_-_Finanzas.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-LE-D1</t>
+          <t>GE-SO-IT-D1</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Help Desk</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Asistente Legal (11) · Analista Legal (10) · Coordinador/a de Asuntos Legales (10)</t>
+          <t>Help Desk (10) · Desarrollador JR (6) · Gerente tecnologico (6) · Analista de desarrollo y sistema (5)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>904e5c44-GE-SO-LE-D1_-_Legal.xlsx</t>
+          <t>7794a690-GE-SO-IT-D1_-_IT.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-LE-D1</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Mantenimiento - Administrativos</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>156</v>
+        <v>31</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Gerente JR de mantenimiento (20) · Jefe de mantenimiento (42) · Planificador de mantenimiento (21) · Supervisor de mantenimiento (38) · Auxiliar administrativo (35)</t>
+          <t>Asistente Legal (11) · Analista Legal (10) · Coordinador/a de Asuntos Legales (10)</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>271a4bea-GE-SO-MA-D1_-_Mantenimiento.xlsx</t>
+          <t>904e5c44-GE-SO-LE-D1_-_Legal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PGS-D1</t>
+          <t>GE-SO-MA-D1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Engicore</t>
+          <t>Mantenimiento - Administrativos</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Jefe de Diseño e Ingenieria (9) · Ingeniero de Diseño e Ingenieria (14) · Analista de Diseño e Ingenieria (9)</t>
+          <t>Gerente JR de mantenimiento (20) · Jefe de mantenimiento (42) · Planificador de mantenimiento (21) · Supervisor de mantenimiento (38) · Auxiliar administrativo (35)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>f4a8175b-GE-SO-PGS-D1_-_Engicore.xlsx</t>
+          <t>271a4bea-GE-SO-MA-D1_-_Mantenimiento.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1</t>
+          <t>GE-SO-PGS-D1</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Planificación y Logística</t>
+          <t>Engicore</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Planificación y Logística (11) · Coordinador de Supply Chain (6) · Programador de Producción (8) · Analista de Supply Chain (6)</t>
+          <t>Jefe de Diseño e Ingenieria (9) · Ingeniero de Diseño e Ingenieria (14) · Analista de Diseño e Ingenieria (9)</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>1fa9982d-GE-SO-PO-D1_-_Planificaci_n_y_Log_stica.xlsx</t>
+          <t>f4a8175b-GE-SO-PGS-D1_-_Engicore.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PY-D1</t>
+          <t>GE-SO-PO-D1</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Proyectos</t>
+          <t>Planificación y Logística</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Jefe de Proyectos (20) · Ingeniero de Proyectos (15) · Analista de Proyectos (16)</t>
+          <t>Jefe de Planificación y Logística (11) · Coordinador de Supply Chain (6) · Programador de Producción (8) · Analista de Supply Chain (6)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>933cde5a-GE-SO-PY-D1_-_Proyectos.xlsx</t>
+          <t>1fa9982d-GE-SO-PO-D1_-_Planificaci_n_y_Log_stica.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-SC-D1</t>
+          <t>GE-SO-PY-D1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Compras</t>
+          <t>Proyectos</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Analista Supply Chain (13) · Analista Compras (14) · Jefe de Compras (13)</t>
+          <t>Jefe de Proyectos (20) · Ingeniero de Proyectos (15) · Analista de Proyectos (16)</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>9c752964-GE-SO-SC-D1_-_Compras.xlsx</t>
+          <t>933cde5a-GE-SO-PY-D1_-_Proyectos.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-RL-D35</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Salud Ocupacional</t>
+          <t>Operations Mng Staff</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Medico Ocupacional (18) · Enfermero Ocupacional (10) · Auxiliar de servicios de salud (11)</t>
+          <t>Director de Operaciones (14) · Gerente de Producción (16) · Jefe de Producción (MV y Secado) (18) · Auxiliar Administrativo (12)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>cf092d8f-GE-SO-SF-D1_-_Salud_ocupacional.xlsx</t>
+          <t>fe6c6893-Matriz_IPERC_Plantabal_Operations_Mng_Staff.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>RECURSOS HUMANOS</t>
+          <t>Compras</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>339</v>
+        <v>40</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>HR DIRECTOR AMERICAS (36) · HR BUSINNES PARTNER AMERICAS (42) · BUSINNES PARTNER DE RECURSOS HUMANOS (28) · COORDINADORA DE DESARROLLO ORGANIZACIONAL (49) · PEOPLE OPERATIONS PARTNER (42) · ANALISTA DE RECURSOS HUMANOS (72) · ANALISTA DE RECURSOS HUMANOS Y NÓMINA (28) · ANALISTA DE DESARROLLO ORGANIZACIONAL (42)</t>
+          <t>Analista Supply Chain (13) · Analista Compras (14) · Jefe de Compras (13)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>b206b7b5-GE-SO-TH-D1_-_RRHH.xlsx</t>
+          <t>9c752964-GE-SO-SC-D1_-_Compras.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>GE-SO-SF-D1</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Salud Ocupacional</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Medico Ocupacional (18) · Enfermero Ocupacional (10) · Auxiliar de servicios de salud (11)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>cf092d8f-GE-SO-SF-D1_-_Salud_ocupacional.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-TH-D1</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>RECURSOS HUMANOS</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>339</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>HR DIRECTOR AMERICAS (36) · HR BUSINNES PARTNER AMERICAS (42) · BUSINNES PARTNER DE RECURSOS HUMANOS (28) · COORDINADORA DE DESARROLLO ORGANIZACIONAL (49) · PEOPLE OPERATIONS PARTNER (42) · ANALISTA DE RECURSOS HUMANOS (72) · ANALISTA DE RECURSOS HUMANOS Y NÓMINA (28) · ANALISTA DE DESARROLLO ORGANIZACIONAL (42)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>b206b7b5-GE-SO-TH-D1_-_RRHH.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="9" t="n">
-        <v>54</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>1107</v>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>1179</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F20"/>
+  <autoFilter ref="A4:F22"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/Cobertura_IPERC_Administrativos_CAR.xlsx
+++ b/Cobertura_IPERC_Administrativos_CAR.xlsx
@@ -13,14 +13,16 @@
     <sheet name="4. Brechas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5. Observaciones" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="6. Trazabilidad" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7. Cambios del mes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Alcance y criterios'!$A$4:$C$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Alcance y criterios'!$A$4:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Resumen por área'!$A$4:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Matriz consolidada'!$A$4:$J$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$I$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Observaciones'!$A$4:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Matriz consolidada'!$A$4:$J$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Observaciones'!$A$4:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Trazabilidad'!$A$4:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'7. Cambios del mes'!$A$4:$F$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -163,10 +165,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -546,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -627,12 +629,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Exclusión por jerarquía</t>
+          <t>Alcance geográfico</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Se excluyen las jerarquías 'BC Workers' y 'BC Leaders' (personal operativo).</t>
+          <t>Se incluyen las localidades Quevedo y Samborondón. Santo Domingo queda fuera del alcance de este control.</t>
         </is>
       </c>
     </row>
@@ -644,12 +646,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Alcance geográfico</t>
+          <t>Exclusión por dependencia</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Se incluyen las localidades Quevedo y Samborondón.</t>
+          <t>Se excluye al personal con Localidad Principal 'High Point'.</t>
         </is>
       </c>
     </row>
@@ -661,12 +663,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Exclusión por dependencia</t>
+          <t>Clasificación administrativo / operativo</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Se excluye al personal con Localidad Principal 'High Point'.</t>
+          <t>Se aplica el catálogo de cargos 'cargos_administrativos.json', validado cargo por cargo. NO se utiliza la columna de jerarquía del head count: desde el corte de octubre de 2026 esa columna llega desalineada respecto al cargo (jefaturas clasificadas como BC Workers y operarios como Top Management), por lo que no es apta para delimitar el universo.</t>
         </is>
       </c>
     </row>
@@ -678,12 +680,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Cargos de frontera</t>
+          <t>Cargos sin clasificar</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Se mantienen dentro del alcance Supervisor de Producción, Supervisor de Mantenimiento, Chofer, Mensajero, Aprendiz, Jefe de Bodega, Técnico de Inventario, Enfermera/o y Médico Ocupacional.</t>
+          <t>Un cargo que no figure en el catálogo queda FUERA del universo y se reporta en la hoja 'Cargos por clasificar', para su incorporación explícita.</t>
         </is>
       </c>
     </row>
@@ -695,12 +697,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Unidad de análisis</t>
+          <t>Cargos de frontera</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>El cruce se realiza por el par ÁREA + CARGO, dado que existen cargos presentes en más de un área.</t>
+          <t>Se mantienen dentro del alcance Supervisor de Producción, Supervisor de Mantenimiento, Chofer, Aprendiz, Jefe de Bodega, Técnico de Inventario, Enfermera/o y Médico.</t>
         </is>
       </c>
     </row>
@@ -712,17 +714,34 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
+          <t>Unidad de análisis</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>El cruce se realiza por el par ÁREA + CARGO, dado que existen cargos presentes en más de un área.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
           <t>Normalización</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Se neutralizan mayúsculas, tildes, dobles espacios, terminaciones de género y errores de tipeo. Las equivalencias no evidentes están registradas en la hoja 5.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C12"/>
+  <autoFilter ref="A4:C13"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
@@ -819,25 +838,25 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>10</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -864,10 +883,10 @@
         <v>82</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>10</v>
@@ -914,26 +933,26 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>1</v>
@@ -947,33 +966,33 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="7" t="n">
-        <v>100</v>
-      </c>
       <c r="F9" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>CONFORME</t>
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>CON BRECHAS</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1023,7 @@
       <c r="H10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
@@ -1037,7 +1056,7 @@
       <c r="H11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
@@ -1062,15 +1081,15 @@
         <v>100</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
@@ -1083,25 +1102,25 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="G13" s="15" t="n">
         <v>79</v>
       </c>
-      <c r="F13" s="15" t="n">
-        <v>101</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>80</v>
-      </c>
       <c r="H13" s="15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I13" s="14" t="inlineStr"/>
     </row>
@@ -1121,13 +1140,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -1168,7 +1187,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Jerarquía</t>
+          <t>Centro de costo</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1218,7 +1237,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5500 HR</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1226,7 +1245,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1262,7 +1281,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5500 HR</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1270,7 +1289,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1306,7 +1325,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5500 HR</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1314,7 +1333,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1350,7 +1369,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5600 LEGAL</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1358,7 +1377,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1394,7 +1413,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Support Staff</t>
+          <t>5600 LEGAL</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1402,7 +1421,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1430,7 +1449,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
+          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -1438,7 +1457,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>4201 SALUD OCUPACIONAL</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1446,29 +1465,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
+          <t>Auxiliar de servicios de salud</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Evaluado en más de una matriz</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1486,7 +1501,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>5500 HR</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1494,7 +1509,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1530,7 +1545,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5600 LEGAL</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1538,7 +1553,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1566,7 +1581,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
+          <t>COORDINADOR DE SEGURIDAD FISICA</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
@@ -1574,7 +1589,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>1200 PLANTATION MANAGEMENT</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1582,25 +1597,21 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-TH-D1</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
-        </is>
-      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1610,15 +1621,15 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>ENFERMERA/O</t>
+          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>5500 HR</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1626,29 +1637,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-TH-D1</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Enfermero Ocupacional</t>
+          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1658,15 +1665,15 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>HR BUSINESS PARTNER AMERICAS</t>
+          <t>ENFERMERA/O</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>4201 SALUD OCUPACIONAL</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1674,25 +1681,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>HR BUSINNES PARTNER AMERICAS</t>
+          <t>Enfermero Ocupacional</t>
         </is>
       </c>
       <c r="I15" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1702,7 +1713,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>HR DIRECTOR AMERICAS</t>
+          <t>HR BUSINESS PARTNER AMERICAS</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -1710,7 +1721,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Top Management</t>
+          <t>5500 HR</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1718,7 +1729,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1730,11 +1741,11 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>HR DIRECTOR AMERICAS</t>
+          <t>HR BUSINNES PARTNER AMERICAS</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J16" s="5" t="inlineStr"/>
     </row>
@@ -1746,15 +1757,15 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>INGENIERO DE SEGURIDAD  Y AMBIENTE</t>
+          <t>HR DIRECTOR AMERICAS</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5700 ADMINISTRACION</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1762,23 +1773,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-EHS-D1</t>
+          <t>GE-SO-TH-D1</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Ingeniero de seguridad y ambiente</t>
+          <t>HR DIRECTOR AMERICAS</t>
         </is>
       </c>
       <c r="I17" s="6" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
     </row>
@@ -1790,15 +1801,15 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>MÉDICO OCUPACIONAL</t>
+          <t>INGENIERO DE SEGURIDAD  Y AMBIENTE</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>4101 PLANTABAL MANUFACTURING #1</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1806,23 +1817,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-EHS-D1</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Medico Ocupacional</t>
+          <t>Ingeniero de seguridad y ambiente</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J18" s="5" t="inlineStr"/>
     </row>
@@ -1834,7 +1845,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
+          <t>MEDICO</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
@@ -1842,7 +1853,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>4201 SALUD OCUPACIONAL</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1850,35 +1861,39 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-EHS-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Tecnico de seguridad y ambiente</t>
+          <t>Medico Ocupacional</t>
         </is>
       </c>
       <c r="I19" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>ESG/Lab</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE LABORATORIO</t>
+          <t>PEOPLE OPERATIONS PARTNER</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
@@ -1886,7 +1901,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Shift Supervisor</t>
+          <t>5500 HR</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1894,35 +1909,35 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-BL-D1</t>
+          <t>GE-SO-TH-D1</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Supervisor de Laboratorio</t>
+          <t>PEOPLE OPERATIONS PARTNER</t>
         </is>
       </c>
       <c r="I20" s="9" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="J20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>ESG/Lab</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>TECNICO DE LABORATORIO</t>
+          <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
@@ -1930,7 +1945,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>4101 PLANTABAL MANUFACTURING #1</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1938,43 +1953,43 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-BL-D1</t>
+          <t>GE-SO-EHS-D1</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Técnico de Laboratorio</t>
+          <t>Tecnico de seguridad y ambiente</t>
         </is>
       </c>
       <c r="I21" s="6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Engicore</t>
+          <t>ESG/Lab</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE DISEÑO E INGENIERIA</t>
+          <t>SUPERVISOR DE LABORATORIO</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5210 LABORATORIO DE BALSA</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -1982,19 +1997,19 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PGS-D1</t>
+          <t>GE-SO-BL-D1</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Analista de Diseño e Ingenieria</t>
+          <t>Supervisor de Laboratorio</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -2005,12 +2020,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Engicore</t>
+          <t>ESG/Lab</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>INGENIERO DE DISEÑO</t>
+          <t>TECNICO DE LABORATORIO</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
@@ -2018,7 +2033,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5210 LABORATORIO DE BALSA</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2026,29 +2041,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PGS-D1</t>
+          <t>GE-SO-BL-D1</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Ingeniero de Diseño e Ingenieria</t>
+          <t>Técnico de Laboratorio</t>
         </is>
       </c>
       <c r="I23" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2058,15 +2069,15 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE DISEÑO E INGENIERIA</t>
+          <t>ANALISTA DE DISEÑO E INGENIERIA</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>4011 DISEÑO E INGENIERIA-PGS</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2074,7 +2085,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2086,7 +2097,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Jefe de Diseño e Ingenieria</t>
+          <t>Analista de Diseño e Ingenieria</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -2097,12 +2108,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>Engicore</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CHOFER</t>
+          <t>INGENIERO DE DISEÑO</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
@@ -2110,39 +2121,47 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>4011 DISEÑO E INGENIERIA-PGS</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Samborondon</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr"/>
+          <t>Quevedo</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-PGS-D1</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Ingeniero de Diseño e Ingenieria</t>
+        </is>
+      </c>
       <c r="I25" s="6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Requiere elaboración de matriz IPERC</t>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>Engicore</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>GERENTE GENERAL</t>
+          <t>JEFE DE DISEÑO E INGENIERIA</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
@@ -2150,7 +2169,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Top Management</t>
+          <t>5006 PGS-ENGICORE AMERICAS</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2158,31 +2177,35 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-PGS-D1</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Jefe de Diseño e Ingenieria</t>
+        </is>
+      </c>
       <c r="I26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>CHOFER</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
@@ -2190,7 +2213,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2217,12 +2240,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE IMPUESTOS</t>
+          <t>GERENTE GENERAL</t>
         </is>
       </c>
       <c r="C28" s="9" t="n">
@@ -2230,12 +2253,12 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
@@ -2257,12 +2280,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE REDES</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
@@ -2270,7 +2293,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5930 3ACM Expenses</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2302,7 +2325,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA FINANCIERO</t>
+          <t>ANALISTA DE IMPUESTOS</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
@@ -2310,7 +2333,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2318,25 +2341,21 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-FI-D1</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>Analista financiero</t>
-        </is>
-      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2346,7 +2365,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>ASISTENTE DE DESARROLLO DE SISTEMA</t>
+          <t>ANALISTA FINANCIERO</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -2354,7 +2373,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Support Staff</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2362,29 +2381,25 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-IT-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Analista de desarrollo y sistema</t>
+          <t>Analista financiero</t>
         </is>
       </c>
       <c r="I31" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2394,15 +2409,15 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>COORDINADOR CONTABLE</t>
+          <t>ASISTENTE DE DESARROLLO DE SISTEMA</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2410,25 +2425,29 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-IT-D1</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Coordinador Contable</t>
+          <t>Analista de desarrollo y sistema</t>
         </is>
       </c>
       <c r="I32" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="5" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2438,15 +2457,15 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR CONTABLE Y DE IMPUESTOS</t>
+          <t>COORDINADOR CONTABLE</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -2454,7 +2473,7 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2466,11 +2485,11 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Coordinador Contable y de Impuestos</t>
+          <t>Coordinador Contable</t>
         </is>
       </c>
       <c r="I33" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J33" s="4" t="inlineStr"/>
     </row>
@@ -2482,7 +2501,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>DESARROLLADOR JR</t>
+          <t>COORDINADOR CONTABLE Y DE IMPUESTOS</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
@@ -2490,7 +2509,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2498,23 +2517,23 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F34" s="13" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-IT-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>Desarrollador JR</t>
+          <t>Coordinador Contable y de Impuestos</t>
         </is>
       </c>
       <c r="I34" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J34" s="5" t="inlineStr"/>
     </row>
@@ -2526,15 +2545,15 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>DIRECTOR FINANCIERO</t>
+          <t>DESARROLLADOR JR</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Top Management</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -2542,21 +2561,25 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr"/>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-IT-D1</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Desarrollador JR</t>
+        </is>
+      </c>
       <c r="I35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -2566,7 +2589,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>GERENTE FINANCIERO</t>
+          <t>DIRECTOR FINANCIERO</t>
         </is>
       </c>
       <c r="C36" s="9" t="n">
@@ -2574,7 +2597,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Middle Management</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2606,7 +2629,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>HELP DESK</t>
+          <t>GERENTE FINANCIERO</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
@@ -2614,33 +2637,29 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-IT-D1</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>Help Desk</t>
-        </is>
-      </c>
+          <t>Samborondon</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2650,7 +2669,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
+          <t>HELP DESK</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
@@ -2658,29 +2677,33 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
+          <t>Quevedo</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-IT-D1</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Help Desk</t>
+        </is>
+      </c>
       <c r="I38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -2690,7 +2713,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
@@ -2698,7 +2721,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -2730,7 +2753,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>MENSAJERO / REPARTIDOR</t>
+          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
@@ -2738,7 +2761,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2746,21 +2769,25 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-FI-D1</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Jefe de Contabilidad e Impuestos</t>
+        </is>
+      </c>
       <c r="I40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -2770,7 +2797,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>REGIONAL IT  MANAGER</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
@@ -2778,7 +2805,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Middle Management</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -2786,27 +2813,19 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-IT-D1</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Gerente tecnologico</t>
-        </is>
-      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+          <t>Requiere elaboración de matriz IPERC</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2837,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>SENIOR BUSINESS CONTROLLER</t>
+          <t>REGIONAL IT  MANAGER</t>
         </is>
       </c>
       <c r="C42" s="9" t="n">
@@ -2826,7 +2845,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2834,31 +2853,39 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr"/>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-IT-D1</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Gerente tecnologico</t>
+        </is>
+      </c>
       <c r="I42" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Requiere elaboración de matriz IPERC</t>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Operaciones</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE COMPRAS</t>
+          <t>SENIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
@@ -2866,35 +2893,27 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-SC-D1</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>Analista Compras</t>
-        </is>
-      </c>
+          <t>Samborondon</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+          <t>Requiere elaboración de matriz IPERC</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2925,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE INVENTARIO</t>
+          <t>ANALISTA DE COMPRAS</t>
         </is>
       </c>
       <c r="C44" s="9" t="n">
@@ -2914,7 +2933,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>4400 PLANTABAL PURCHASE</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -2922,25 +2941,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F44" s="13" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-CI-D1</t>
+          <t>GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Analista de Inventario</t>
+          <t>Analista Compras</t>
         </is>
       </c>
       <c r="I44" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J44" s="5" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2950,7 +2973,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE PROYECTOS</t>
+          <t>ANALISTA DE INVENTARIO</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
@@ -2958,7 +2981,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>4950 INVENTARY</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -2966,23 +2989,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F45" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PY-D1</t>
+          <t>GE-SO-CI-D1</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Analista de Proyectos</t>
+          <t>Analista de Inventario</t>
         </is>
       </c>
       <c r="I45" s="6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J45" s="4" t="inlineStr"/>
     </row>
@@ -2994,45 +3017,41 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE SUPPLY CHAIN</t>
+          <t>ANALISTA DE PROYECTOS</t>
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>4600 PROYECTOS</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Quevedo / Samborondon</t>
-        </is>
-      </c>
-      <c r="F46" s="13" t="inlineStr">
+          <t>Quevedo</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1 / GE-SO-SC-D1</t>
+          <t>GE-SO-PY-D1</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Analista Supply Chain / Analista de Supply Chain</t>
+          <t>Analista de Proyectos</t>
         </is>
       </c>
       <c r="I46" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>Evaluado en más de una matriz</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -3042,35 +3061,43 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>APRENDIZ</t>
+          <t>ANALISTA DE SUPPLY CHAIN</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>4300 PLANTABAL SCH / 4400 PLANTABAL PURCHASE</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr"/>
-      <c r="H47" s="4" t="inlineStr"/>
+          <t>Quevedo / Samborondon</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-PO-D1 / GE-SO-SC-D1</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Analista Supply Chain / Analista de Supply Chain</t>
+        </is>
+      </c>
       <c r="I47" s="6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Requiere elaboración de matriz IPERC</t>
+          <t>Evaluado en más de una matriz</t>
         </is>
       </c>
     </row>
@@ -3082,15 +3109,15 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
+          <t>APRENDIZ</t>
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>3801 PLANTABAL MANTENANCE #1</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3098,27 +3125,19 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
-        </is>
-      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="9" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Evaluado en más de una matriz</t>
+          <t>Requiere elaboración de matriz IPERC</t>
         </is>
       </c>
     </row>
@@ -3130,15 +3149,15 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR DE SUPPLY CHAIN</t>
+          <t>AUXILIAR ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>3158 PROYECTO W / 3251 PLANTABAL D100 #1 / 4800 PLANTABAL OPERATIONS MNG STAFF / 4808 MAINTENANCE MNG STAFF / 5918 PGS</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -3146,25 +3165,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="F49" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1</t>
+          <t>GE-SO-MA-D1 / GE-SO-RL-D35</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Coordinador de Supply Chain</t>
+          <t>Auxiliar Administrativo / Auxiliar administrativo</t>
         </is>
       </c>
       <c r="I49" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada) | Evaluado en más de una matriz</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -3174,7 +3197,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>DIRECTOR DE OPERACIONES</t>
+          <t>COORDINADOR DE SUPPLY CHAIN</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
@@ -3182,7 +3205,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Top Management</t>
+          <t>4300 PLANTABAL SCH</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3190,23 +3213,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="F50" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-RL-D35</t>
+          <t>GE-SO-PO-D1</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>Director de Operaciones</t>
+          <t>Coordinador de Supply Chain</t>
         </is>
       </c>
       <c r="I50" s="9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J50" s="5" t="inlineStr"/>
     </row>
@@ -3218,7 +3241,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>GERENTE DE PRODUCCION</t>
+          <t>DIRECTOR DE OPERACIONES</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
@@ -3226,7 +3249,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Middle Management</t>
+          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -3234,7 +3257,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="F51" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3246,11 +3269,11 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Gerente de Producción</t>
+          <t>Director de Operaciones</t>
         </is>
       </c>
       <c r="I51" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J51" s="4" t="inlineStr"/>
     </row>
@@ -3262,7 +3285,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>GERENTE JR DE MANTENIMIENTO</t>
+          <t>GERENTE DE PRODUCCION</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
@@ -3270,7 +3293,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Middle Management</t>
+          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -3278,23 +3301,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-RL-D35</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>Gerente JR de mantenimiento</t>
+          <t>Gerente de Producción</t>
         </is>
       </c>
       <c r="I52" s="9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J52" s="5" t="inlineStr"/>
     </row>
@@ -3306,7 +3329,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>INGENIERO DE PROYECTOS</t>
+          <t>GERENTE JR DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
@@ -3314,7 +3337,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -3322,23 +3345,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="F53" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PY-D1</t>
+          <t>GE-SO-MA-D1</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Ingeniero de Proyectos</t>
+          <t>Gerente JR de mantenimiento</t>
         </is>
       </c>
       <c r="I53" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J53" s="4" t="inlineStr"/>
     </row>
@@ -3350,7 +3373,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE BODEGA</t>
+          <t>INGENIERO DE PROYECTOS</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
@@ -3358,7 +3381,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>4600 PROYECTOS</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -3366,21 +3389,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F54" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr"/>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-PY-D1</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Ingeniero de Proyectos</t>
+        </is>
+      </c>
       <c r="I54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -3390,7 +3417,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE COMPRAS E IMPORTACIONES</t>
+          <t>JEFE DE BODEGA</t>
         </is>
       </c>
       <c r="C55" s="6" t="n">
@@ -3398,7 +3425,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>2500 SERVICE CENTER</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -3406,27 +3433,19 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-SC-D1</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>Jefe de Compras</t>
-        </is>
-      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
       <c r="I55" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+          <t>Requiere elaboración de matriz IPERC</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3457,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE MANTENIMIENTO</t>
+          <t>JEFE DE COMPRAS E IMPORTACIONES</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
@@ -3446,7 +3465,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>4400 PLANTABAL PURCHASE</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -3454,25 +3473,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F56" s="13" t="inlineStr">
+      <c r="F56" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>Jefe de mantenimiento</t>
+          <t>Jefe de Compras</t>
         </is>
       </c>
       <c r="I56" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="J56" s="5" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -3482,7 +3505,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE PLANIFICACION Y LOGISTICA</t>
+          <t>JEFE DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C57" s="6" t="n">
@@ -3490,7 +3513,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -3498,23 +3521,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="F57" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1</t>
+          <t>GE-SO-MA-D1</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Planificación y Logística</t>
+          <t>Jefe de mantenimiento</t>
         </is>
       </c>
       <c r="I57" s="6" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="J57" s="4" t="inlineStr"/>
     </row>
@@ -3526,7 +3549,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE PRODUCCION</t>
+          <t>JEFE DE PLANIFICACION Y LOGISTICA</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
@@ -3534,7 +3557,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>4300 PLANTABAL SCH</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -3542,21 +3565,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="5" t="inlineStr"/>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-PO-D1</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Jefe de Planificación y Logística</t>
+        </is>
+      </c>
       <c r="I58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -3566,7 +3593,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE PROYECTOS</t>
+          <t>JEFE DE PRODUCCION</t>
         </is>
       </c>
       <c r="C59" s="6" t="n">
@@ -3574,7 +3601,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -3582,25 +3609,21 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-PY-D1</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>Jefe de Proyectos</t>
-        </is>
-      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr"/>
       <c r="I59" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -3610,7 +3633,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>PLANIFICADOR DE MANTENIMIENTO</t>
+          <t>JEFE DE PROYECTOS</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
@@ -3618,7 +3641,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>4600 PROYECTOS</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -3626,23 +3649,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F60" s="13" t="inlineStr">
+      <c r="F60" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-PY-D1</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>Planificador de mantenimiento</t>
+          <t>Jefe de Proyectos</t>
         </is>
       </c>
       <c r="I60" s="9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J60" s="5" t="inlineStr"/>
     </row>
@@ -3654,7 +3677,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>PROGRAMADOR DE PRODUCCCION</t>
+          <t>PLANIFICADOR DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
@@ -3662,7 +3685,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -3670,23 +3693,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr">
+      <c r="F61" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1</t>
+          <t>GE-SO-MA-D1</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Programador de Producción</t>
+          <t>Planificador de mantenimiento</t>
         </is>
       </c>
       <c r="I61" s="6" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J61" s="4" t="inlineStr"/>
     </row>
@@ -3698,15 +3721,15 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE MANTENIMIENTO</t>
+          <t>PROGRAMADOR DE PRODUCCCION</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Shift Supervisor</t>
+          <t>4300 PLANTABAL SCH</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -3714,23 +3737,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F62" s="13" t="inlineStr">
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-PO-D1</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>Supervisor de mantenimiento</t>
+          <t>Programador de Producción</t>
         </is>
       </c>
       <c r="I62" s="9" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="J62" s="5" t="inlineStr"/>
     </row>
@@ -3742,15 +3765,15 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE PRODUCCIÓN</t>
+          <t>SUPERVISOR DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Shift Supervisor</t>
+          <t>4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3758,21 +3781,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F63" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr"/>
-      <c r="H63" s="4" t="inlineStr"/>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-MA-D1</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor de mantenimiento</t>
+        </is>
+      </c>
       <c r="I63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -3782,15 +3809,15 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>TECNICO DE INVENTARIO</t>
+          <t>SUPERVISOR DE PRODUCCIÓN</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>3010 KITS PRODUCTION - PGS / 3821 SUP DE PRODUCCION</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -3798,43 +3825,39 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F64" s="13" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-CI-D1</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>Técnico de Inventario</t>
-        </is>
-      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="J64" s="5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>QSE &amp; Operational Excellence</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE CALIDAD</t>
+          <t>TECNICO DE INVENTARIO</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>4950 INVENTARY</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3842,23 +3865,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F65" s="12" t="inlineStr">
+      <c r="F65" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-CC-D1</t>
+          <t>GE-SO-CI-D1</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Analista de calidad</t>
+          <t>Técnico de Inventario</t>
         </is>
       </c>
       <c r="I65" s="6" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="J65" s="4" t="inlineStr"/>
     </row>
@@ -3870,15 +3893,15 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>COORDINADOR DE CALIDAD</t>
+          <t>ANALISTA DE CALIDAD</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>4500 PLANTABAL QUALITY</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -3886,7 +3909,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F66" s="13" t="inlineStr">
+      <c r="F66" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3898,7 +3921,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>Coordinador de calidad</t>
+          <t>Analista de calidad</t>
         </is>
       </c>
       <c r="I66" s="9" t="n">
@@ -3914,15 +3937,15 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR DE EXCELENCIA OPERACIONAL</t>
+          <t>COORDINADOR DE CALIDAD</t>
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>4500 PLANTABAL QUALITY</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3930,23 +3953,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F67" s="12" t="inlineStr">
+      <c r="F67" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-EO-D1</t>
+          <t>GE-SO-CC-D1</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Coordinador de Excelencia Operacional</t>
+          <t>Coordinador de calidad</t>
         </is>
       </c>
       <c r="I67" s="6" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="J67" s="4" t="inlineStr"/>
     </row>
@@ -3958,15 +3981,15 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>COORDINADORA DE CERTIFICACIONES</t>
+          <t>COORDINADOR DE EXCELENCIA OPERACIONAL</t>
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>4650 EXCELENCIA OPERACIONAL</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -3974,23 +3997,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F68" s="13" t="inlineStr">
+      <c r="F68" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-CE-D1</t>
+          <t>GE-SO-EO-D1</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>Coordinador/a de Certificaciones</t>
+          <t>Coordinador de Excelencia Operacional</t>
         </is>
       </c>
       <c r="I68" s="9" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J68" s="5" t="inlineStr"/>
     </row>
@@ -4002,7 +4025,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>ESPECIALISTA DE CERTIFICACIONES</t>
+          <t>COORDINADORA DE CERTIFICACIONES</t>
         </is>
       </c>
       <c r="C69" s="6" t="n">
@@ -4010,7 +4033,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>4350 CERTIFICACION FSC</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -4018,7 +4041,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F69" s="12" t="inlineStr">
+      <c r="F69" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -4030,11 +4053,11 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Especialista de Certificaciones</t>
+          <t>Coordinador/a de Certificaciones</t>
         </is>
       </c>
       <c r="I69" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J69" s="4" t="inlineStr"/>
     </row>
@@ -4046,7 +4069,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>GERENTE DE CALIDAD Y CERTIFICACIONES</t>
+          <t>ESPECIALISTA DE CERTIFICACIONES</t>
         </is>
       </c>
       <c r="C70" s="9" t="n">
@@ -4054,7 +4077,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Middle Management</t>
+          <t>4350 CERTIFICACION FSC</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -4062,29 +4085,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F70" s="13" t="inlineStr">
+      <c r="F70" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-CC-D1</t>
+          <t>GE-SO-CE-D1</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>QSE &amp; Operational Excellence Manager</t>
+          <t>Especialista de Certificaciones</t>
         </is>
       </c>
       <c r="I70" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="J70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -4094,15 +4113,15 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>INGENIERO DE SEGURIDAD  Y AMBIENTE</t>
+          <t>GERENTE DE CALIDAD Y CERTIFICACIONES</t>
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>4500 PLANTABAL QUALITY</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -4110,25 +4129,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F71" s="12" t="inlineStr">
+      <c r="F71" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-EHS-D1</t>
+          <t>GE-SO-CC-D1</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Ingeniero de seguridad y ambiente</t>
+          <t>QSE &amp; Operational Excellence Manager</t>
         </is>
       </c>
       <c r="I71" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -4138,15 +4161,15 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>TECNICO DE CALIDAD</t>
+          <t>INGENIERO DE SEGURIDAD  Y AMBIENTE</t>
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>4203 SEGURIDAD OCUPACIONAL Y AMBIENTE</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -4154,23 +4177,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F72" s="13" t="inlineStr">
+      <c r="F72" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-CC-D1</t>
+          <t>GE-SO-EHS-D1</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>Técnico de calidad</t>
+          <t>Ingeniero de seguridad y ambiente</t>
         </is>
       </c>
       <c r="I72" s="9" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="J72" s="5" t="inlineStr"/>
     </row>
@@ -4182,15 +4205,15 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>TECNICO DE CERTIFICACIONES</t>
+          <t>TECNICO DE CALIDAD</t>
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>4500 PLANTABAL QUALITY / 4507 QUALITY SD</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -4198,23 +4221,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F73" s="12" t="inlineStr">
+      <c r="F73" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-CE-D1</t>
+          <t>GE-SO-CC-D1</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Técnico de Certificaciones</t>
+          <t>Técnico de calidad</t>
         </is>
       </c>
       <c r="I73" s="6" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="J73" s="4" t="inlineStr"/>
     </row>
@@ -4226,44 +4249,88 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
+          <t>TECNICO DE CERTIFICACIONES</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>4350 CERTIFICACION FSC</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Quevedo</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-CE-D1</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Técnico de Certificaciones</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="J74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>QSE &amp; Operational Excellence</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
           <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
         </is>
       </c>
-      <c r="C74" s="9" t="n">
+      <c r="C75" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>BC Adm</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>4203 SEGURIDAD OCUPACIONAL Y AMBIENTE</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F74" s="13" t="inlineStr">
+      <c r="F75" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>GE-SO-EHS-D1</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>Tecnico de seguridad y ambiente</t>
         </is>
       </c>
-      <c r="I74" s="9" t="n">
+      <c r="I75" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="J74" s="5" t="inlineStr"/>
+      <c r="J75" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J74"/>
+  <autoFilter ref="A4:J75"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -4278,18 +4345,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4324,30 +4390,25 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Jerarquía</t>
+          <t>Localidad</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Localidad</t>
+          <t>Centro de costo</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Centro de costo</t>
+          <t>Acción requerida</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Acción requerida</t>
+          <t>Responsable</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Fecha compromiso</t>
         </is>
@@ -4369,36 +4430,31 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Shift Supervisor</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>3010 KITS PRODUCTION - PGS / 3821 SUP DE PRODUCCION</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>3010 KITS PRODUCTION - PGS / 3821 SUP DE PRODUCCION</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>CHOFER</t>
+          <t>COORDINADOR DE SEGURIDAD FISICA</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
@@ -4406,26 +4462,21 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>1200 PLANTATION MANAGEMENT</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -4435,7 +4486,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>GERENTE GENERAL</t>
+          <t>CHOFER</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -4443,36 +4494,31 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Top Management</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>GERENTE GENERAL</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
@@ -4480,36 +4526,31 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>5930 3ACM Expenses</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>ANALISTA DE IMPUESTOS</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
@@ -4517,26 +4558,21 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>5930 3ACM Expenses</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -4546,7 +4582,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>ANALISTA DE REDES</t>
+          <t>ANALISTA DE IMPUESTOS</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -4554,26 +4590,21 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>5400 IT</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -4591,26 +4622,21 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Top Management</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -4628,26 +4654,21 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Middle Management</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -4665,26 +4686,21 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>5400 IT</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -4702,26 +4718,21 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -4731,7 +4742,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>MENSAJERO / REPARTIDOR</t>
+          <t>SENIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
@@ -4739,36 +4750,31 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>SENIOR BUSINESS CONTROLLER</t>
+          <t>APRENDIZ</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -4776,26 +4782,21 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Professional</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>3801 PLANTABAL MANTENANCE #1</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -4805,7 +4806,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>APRENDIZ</t>
+          <t>JEFE DE BODEGA</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
@@ -4813,26 +4814,21 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>BC Adm</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>2500 SERVICE CENTER</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>3801 PLANTABAL MANTENANCE #1</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -4842,7 +4838,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>JEFE DE BODEGA</t>
+          <t>JEFE DE PRODUCCION</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
@@ -4850,69 +4846,27 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Low Management</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2500 SERVICE CENTER</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
       </c>
+      <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Operaciones</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>JEFE DE PRODUCCION</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Low Management</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Elaborar matriz IPERC para el puesto</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I19"/>
+  <autoFilter ref="A4:H18"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4924,7 +4878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5106,12 +5060,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
+          <t>ENFERMERO OCUPACIONAL</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
+          <t>ENFERMERA/O</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -5126,7 +5080,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>En el head count consta como AUXILIAR ADMINISTRATIVO. La denominacion 'Auxiliar de servicios de salud' se uso solo a efectos de la matriz de Salud Ocupacional. Corresponde al auxiliar administrativo asignado a ADM-L&amp;RH (1 persona); los 5 de Operaciones estan cubiertos por GE-SO-MA-D1.</t>
+          <t>Misma funcion, denominacion en masculino/ocupacional</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -5138,22 +5092,22 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-IT-D1</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ENFERMERO OCUPACIONAL</t>
+          <t>GERENTE TECNOLOGICO</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>ENFERMERA/O</t>
+          <t>REGIONAL IT  MANAGER</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -5163,7 +5117,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Misma funcion, denominacion en masculino/ocupacional</t>
+          <t>Mismo puesto, denominacion distinta</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -5175,22 +5129,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-IT-D1</t>
+          <t>GE-SO-PGS-D1</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>GERENTE TECNOLOGICO</t>
+          <t>INGENIERO DE DISENO E INGENIERIA</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>REGIONAL IT  MANAGER</t>
+          <t>INGENIERO DE DISEÑO</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Engicore</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -5200,7 +5154,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Mismo puesto, denominacion distinta</t>
+          <t>Mismo puesto</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -5212,22 +5166,22 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PGS-D1</t>
+          <t>GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>INGENIERO DE DISENO E INGENIERIA</t>
+          <t>JEFE DE COMPRAS</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>INGENIERO DE DISEÑO</t>
+          <t>JEFE DE COMPRAS E IMPORTACIONES</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Engicore</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -5237,7 +5191,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Mismo puesto</t>
+          <t>Mismo puesto, confirmado por Hector</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -5249,22 +5203,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SC-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE COMPRAS</t>
+          <t>MEDICO OCUPACIONAL</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE COMPRAS E IMPORTACIONES</t>
+          <t>MEDICO</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Operaciones</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -5274,7 +5228,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Mismo puesto, confirmado por Hector</t>
+          <t>El head count de octubre 2026 renombro el cargo de MEDICO OCUPACIONAL a MEDICO</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -5323,145 +5277,182 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
+          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>(no consta)</t>
+          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Cargo nuevo no registrado</t>
+          <t>Regularizado - cerrado</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>ANALIZADO en matriz / NO CONSTA en head count V1.1</t>
+          <t>REGULARIZADO - consta en el head count de octubre 2026 con la misma denominacion de la matriz</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Incorporar el cargo a la base de head count</t>
+          <t>Ninguna. Accion correctiva cumplida.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>PEOPLE OPERATIONS PARTNER</t>
+          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>(no consta)</t>
+          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Cargo nuevo no registrado</t>
+          <t>Regularizado - cerrado</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>ANALIZADO en matriz / NO CONSTA en head count V1.1</t>
+          <t>REGULARIZADO - consta en el head count de octubre 2026</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Incorporar el cargo a la base de head count</t>
+          <t>Ninguna. Accion correctiva cumplida.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-TH-D1</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>COORDINADOR DE TESORERIA</t>
+          <t>PEOPLE OPERATIONS PARTNER</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>(no existe)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr"/>
+          <t>PEOPLE OPERATIONS PARTNER</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Cargo obsoleto</t>
+          <t>Regularizado - cerrado</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>CARGO INEXISTENTE - suprimido de la estructura</t>
+          <t>REGULARIZADO - consta en el head count de octubre 2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>ELIMINAR el bloque completo de la matriz GE-SO-FI-D1</t>
+          <t>Ninguna. Accion correctiva cumplida.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-RL-D35</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Producción (MV y Secado)</t>
+          <t>COORDINADOR DE TESORERIA</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>(no consta)</t>
+          <t>(no existe)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
+          <t>Cargo obsoleto</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>CARGO INEXISTENTE - suprimido de la estructura</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>ELIMINAR el bloque completo de la matriz GE-SO-FI-D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-RL-D35</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Jefe de Producción (MV y Secado)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>(no consta)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>SIN CLASIFICAR - detectado este mes</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Puesto evaluado en la matriz que no aparece en el head count del mes</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Definir si es cargo nuevo, denominación alterna o cargo suprimido</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G17"/>
+  <autoFilter ref="A4:G18"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -6033,4 +6024,409 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CAMBIOS RESPECTO AL CORTE ANTERIOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tipo de cambio</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Área</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>N° personas</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Estado de cobertura</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Acción sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ALTA - cargo nuevo</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verificar cobertura</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ALTA - cargo nuevo</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>COORDINADOR DE SEGURIDAD FISICA</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verificar cobertura</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ALTA - cargo nuevo</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>MEDICO</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verificar cobertura</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ALTA - cargo nuevo</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>PEOPLE OPERATIONS PARTNER</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verificar cobertura</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>VARIACIÓN de dotación (2 → 1)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>IT&amp;FIN</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>COORDINADOR CONTABLE</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Sin acción si el cargo ya está cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ALTA - cargo nuevo</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>IT&amp;FIN</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Verificar cobertura</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>VARIACIÓN de dotación (3 → 2)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Operaciones</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>TECNICO DE INVENTARIO</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Sin acción si el cargo ya está cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>VARIACIÓN de dotación (4 → 3)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>QSE &amp; Operational Excellence</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>TECNICO DE CALIDAD</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Sin acción si el cargo ya está cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>BAJA - cargo ya no consta</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>AUXILIAR ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>BAJA - cargo ya no consta</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>MÉDICO OCUPACIONAL</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BAJA - cargo ya no consta</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>IT&amp;FIN</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>ANALISTA DE REDES</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>BAJA - cargo ya no consta</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>IT&amp;FIN</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>MENSAJERO / REPARTIDOR</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F16"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Cobertura_IPERC_Administrativos_CAR.xlsx
+++ b/Cobertura_IPERC_Administrativos_CAR.xlsx
@@ -13,16 +13,14 @@
     <sheet name="4. Brechas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5. Observaciones" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="6. Trazabilidad" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7. Cambios del mes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Alcance y criterios'!$A$4:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Resumen por área'!$A$4:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Matriz consolidada'!$A$4:$J$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Observaciones'!$A$4:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Matriz consolidada'!$A$4:$J$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Observaciones'!$A$4:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Trazabilidad'!$A$4:$F$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'7. Cambios del mes'!$A$4:$F$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -165,10 +163,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -838,25 +836,25 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="E5" s="7" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>10</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -883,10 +881,10 @@
         <v>82</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>10</v>
@@ -933,26 +931,26 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>1</v>
@@ -966,33 +964,33 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C9" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="E9" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>CON BRECHAS</t>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1021,7 @@
       <c r="H10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
@@ -1056,7 +1054,7 @@
       <c r="H11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
@@ -1081,15 +1079,15 @@
         <v>100</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
@@ -1102,25 +1100,25 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="16" t="n">
+        <v>79</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>101</v>
+      </c>
+      <c r="G13" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="F13" s="15" t="n">
-        <v>99</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>79</v>
-      </c>
       <c r="H13" s="15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I13" s="14" t="inlineStr"/>
     </row>
@@ -1140,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1245,7 +1243,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1289,7 +1287,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1333,7 +1331,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1377,7 +1375,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1421,7 +1419,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1449,7 +1447,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
+          <t>AUXILIAR ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -1465,25 +1463,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Auxiliar de servicios de salud</t>
+          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Evaluado en más de una matriz</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1509,7 +1511,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1553,7 +1555,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1581,7 +1583,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR DE SEGURIDAD FISICA</t>
+          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
@@ -1589,7 +1591,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>1200 PLANTATION MANAGEMENT</t>
+          <t>5500 HR</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1597,21 +1599,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr"/>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-TH-D1</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1621,15 +1627,15 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
+          <t>ENFERMERA/O</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>5500 HR</t>
+          <t>4201 SALUD OCUPACIONAL</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1637,25 +1643,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
+          <t>Enfermero Ocupacional</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>49</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1665,15 +1675,15 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ENFERMERA/O</t>
+          <t>HR BUSINESS PARTNER AMERICAS</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>4201 SALUD OCUPACIONAL</t>
+          <t>5500 HR</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1681,29 +1691,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-TH-D1</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Enfermero Ocupacional</t>
+          <t>HR BUSINNES PARTNER AMERICAS</t>
         </is>
       </c>
       <c r="I15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1713,7 +1719,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>HR BUSINESS PARTNER AMERICAS</t>
+          <t>HR DIRECTOR AMERICAS</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -1721,7 +1727,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>5500 HR</t>
+          <t>5700 ADMINISTRACION</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1729,7 +1735,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1741,11 +1747,11 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>HR BUSINNES PARTNER AMERICAS</t>
+          <t>HR DIRECTOR AMERICAS</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J16" s="5" t="inlineStr"/>
     </row>
@@ -1757,15 +1763,15 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>HR DIRECTOR AMERICAS</t>
+          <t>INGENIERO DE SEGURIDAD  Y AMBIENTE</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>5700 ADMINISTRACION</t>
+          <t>4101 PLANTABAL MANUFACTURING #1</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1773,23 +1779,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-EHS-D1</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>HR DIRECTOR AMERICAS</t>
+          <t>Ingeniero de seguridad y ambiente</t>
         </is>
       </c>
       <c r="I17" s="6" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
     </row>
@@ -1801,15 +1807,15 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>INGENIERO DE SEGURIDAD  Y AMBIENTE</t>
+          <t>MÉDICO OCUPACIONAL</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>4101 PLANTABAL MANUFACTURING #1</t>
+          <t>4201 SALUD OCUPACIONAL</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1817,23 +1823,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-EHS-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Ingeniero de seguridad y ambiente</t>
+          <t>Medico Ocupacional</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J18" s="5" t="inlineStr"/>
     </row>
@@ -1845,7 +1851,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>MEDICO</t>
+          <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
@@ -1853,7 +1859,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>4201 SALUD OCUPACIONAL</t>
+          <t>4101 PLANTABAL MANUFACTURING #1</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1861,39 +1867,35 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-EHS-D1</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Medico Ocupacional</t>
+          <t>Tecnico de seguridad y ambiente</t>
         </is>
       </c>
       <c r="I19" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>ESG/Lab</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>PEOPLE OPERATIONS PARTNER</t>
+          <t>SUPERVISOR DE LABORATORIO</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
@@ -1901,7 +1903,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>5500 HR</t>
+          <t>5210 LABORATORIO DE BALSA</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1909,35 +1911,35 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-BL-D1</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>PEOPLE OPERATIONS PARTNER</t>
+          <t>Supervisor de Laboratorio</t>
         </is>
       </c>
       <c r="I20" s="9" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="J20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>ESG/Lab</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
+          <t>TECNICO DE LABORATORIO</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
@@ -1945,7 +1947,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>4101 PLANTABAL MANUFACTURING #1</t>
+          <t>5210 LABORATORIO DE BALSA</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1953,43 +1955,43 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-EHS-D1</t>
+          <t>GE-SO-BL-D1</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Tecnico de seguridad y ambiente</t>
+          <t>Técnico de Laboratorio</t>
         </is>
       </c>
       <c r="I21" s="6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>ESG/Lab</t>
+          <t>Engicore</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE LABORATORIO</t>
+          <t>ANALISTA DE DISEÑO E INGENIERIA</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>5210 LABORATORIO DE BALSA</t>
+          <t>4011 DISEÑO E INGENIERIA-PGS</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -1997,19 +1999,19 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-BL-D1</t>
+          <t>GE-SO-PGS-D1</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Supervisor de Laboratorio</t>
+          <t>Analista de Diseño e Ingenieria</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -2020,12 +2022,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>ESG/Lab</t>
+          <t>Engicore</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>TECNICO DE LABORATORIO</t>
+          <t>INGENIERO DE DISEÑO</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
@@ -2033,7 +2035,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5210 LABORATORIO DE BALSA</t>
+          <t>4011 DISEÑO E INGENIERIA-PGS</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2041,25 +2043,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-BL-D1</t>
+          <t>GE-SO-PGS-D1</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Técnico de Laboratorio</t>
+          <t>Ingeniero de Diseño e Ingenieria</t>
         </is>
       </c>
       <c r="I23" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2069,15 +2075,15 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE DISEÑO E INGENIERIA</t>
+          <t>JEFE DE DISEÑO E INGENIERIA</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>4011 DISEÑO E INGENIERIA-PGS</t>
+          <t>5006 PGS-ENGICORE AMERICAS</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2085,7 +2091,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2097,7 +2103,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Analista de Diseño e Ingenieria</t>
+          <t>Jefe de Diseño e Ingenieria</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -2108,12 +2114,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Engicore</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>INGENIERO DE DISEÑO</t>
+          <t>CHOFER</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
@@ -2121,47 +2127,39 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4011 DISEÑO E INGENIERIA-PGS</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-PGS-D1</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Ingeniero de Diseño e Ingenieria</t>
-        </is>
-      </c>
+          <t>Samborondon</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+          <t>Requiere elaboración de matriz IPERC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Engicore</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE DISEÑO E INGENIERIA</t>
+          <t>GERENTE GENERAL</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
@@ -2169,7 +2167,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>5006 PGS-ENGICORE AMERICAS</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2177,35 +2175,31 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-PGS-D1</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>Jefe de Diseño e Ingenieria</t>
-        </is>
-      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J26" s="5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>CHOFER</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
@@ -2213,7 +2207,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
+          <t>5930 3ACM Expenses</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2240,12 +2234,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>GERENTE GENERAL</t>
+          <t>ANALISTA DE IMPUESTOS</t>
         </is>
       </c>
       <c r="C28" s="9" t="n">
@@ -2253,12 +2247,12 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
@@ -2280,12 +2274,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>ANALISTA DE REDES</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
@@ -2293,7 +2287,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>5930 3ACM Expenses</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2325,7 +2319,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE IMPUESTOS</t>
+          <t>ANALISTA FINANCIERO</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
@@ -2341,21 +2335,25 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-FI-D1</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Analista financiero</t>
+        </is>
+      </c>
       <c r="I30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2365,7 +2363,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA FINANCIERO</t>
+          <t>ASISTENTE DE DESARROLLO DE SISTEMA</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -2373,7 +2371,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2381,25 +2379,29 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-IT-D1</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Analista financiero</t>
+          <t>Analista de desarrollo y sistema</t>
         </is>
       </c>
       <c r="I31" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2409,15 +2411,15 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>ASISTENTE DE DESARROLLO DE SISTEMA</t>
+          <t>COORDINADOR CONTABLE</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2425,29 +2427,25 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-IT-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Analista de desarrollo y sistema</t>
+          <t>Coordinador Contable</t>
         </is>
       </c>
       <c r="I32" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2457,11 +2455,11 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR CONTABLE</t>
+          <t>COORDINADOR CONTABLE Y DE IMPUESTOS</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
@@ -2473,7 +2471,7 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2485,11 +2483,11 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Coordinador Contable</t>
+          <t>Coordinador Contable y de Impuestos</t>
         </is>
       </c>
       <c r="I33" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J33" s="4" t="inlineStr"/>
     </row>
@@ -2501,7 +2499,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>COORDINADOR CONTABLE Y DE IMPUESTOS</t>
+          <t>DESARROLLADOR JR</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
@@ -2509,7 +2507,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2517,23 +2515,23 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-IT-D1</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>Coordinador Contable y de Impuestos</t>
+          <t>Desarrollador JR</t>
         </is>
       </c>
       <c r="I34" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J34" s="5" t="inlineStr"/>
     </row>
@@ -2545,15 +2543,15 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>DESARROLLADOR JR</t>
+          <t>DIRECTOR FINANCIERO</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -2561,25 +2559,21 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F35" s="13" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-IT-D1</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Desarrollador JR</t>
-        </is>
-      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -2589,7 +2583,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>DIRECTOR FINANCIERO</t>
+          <t>GERENTE FINANCIERO</t>
         </is>
       </c>
       <c r="C36" s="9" t="n">
@@ -2629,7 +2623,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>GERENTE FINANCIERO</t>
+          <t>HELP DESK</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
@@ -2637,29 +2631,33 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Samborondon</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr"/>
+          <t>Quevedo</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-IT-D1</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Help Desk</t>
+        </is>
+      </c>
       <c r="I37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2669,7 +2667,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>HELP DESK</t>
+          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
@@ -2682,28 +2680,24 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-IT-D1</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>Help Desk</t>
-        </is>
-      </c>
+          <t>Samborondon</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J38" s="5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -2713,7 +2707,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
@@ -2721,7 +2715,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -2753,7 +2747,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
+          <t>MENSAJERO / REPARTIDOR</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
@@ -2769,25 +2763,21 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-FI-D1</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>Jefe de Contabilidad e Impuestos</t>
-        </is>
-      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J40" s="5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -2797,7 +2787,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>REGIONAL IT  MANAGER</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
@@ -2805,7 +2795,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -2813,19 +2803,27 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr"/>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-IT-D1</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Gerente tecnologico</t>
+        </is>
+      </c>
       <c r="I41" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Requiere elaboración de matriz IPERC</t>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2835,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>REGIONAL IT  MANAGER</t>
+          <t>SENIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C42" s="9" t="n">
@@ -2845,7 +2843,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2853,39 +2851,31 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-IT-D1</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>Gerente tecnologico</t>
-        </is>
-      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+          <t>Requiere elaboración de matriz IPERC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>SENIOR BUSINESS CONTROLLER</t>
+          <t>ANALISTA DE COMPRAS</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
@@ -2893,27 +2883,35 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
+          <t>4400 PLANTABAL PURCHASE</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Samborondon</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
+          <t>Quevedo</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-SC-D1</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Analista Compras</t>
+        </is>
+      </c>
       <c r="I43" s="6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Requiere elaboración de matriz IPERC</t>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2923,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE COMPRAS</t>
+          <t>ANALISTA DE INVENTARIO</t>
         </is>
       </c>
       <c r="C44" s="9" t="n">
@@ -2933,7 +2931,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>4400 PLANTABAL PURCHASE</t>
+          <t>4950 INVENTARY</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -2941,29 +2939,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SC-D1</t>
+          <t>GE-SO-CI-D1</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Analista Compras</t>
+          <t>Analista de Inventario</t>
         </is>
       </c>
       <c r="I44" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2973,7 +2967,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE INVENTARIO</t>
+          <t>ANALISTA DE PROYECTOS</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
@@ -2981,7 +2975,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>4950 INVENTARY</t>
+          <t>4600 PROYECTOS</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -2989,23 +2983,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F45" s="13" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-CI-D1</t>
+          <t>GE-SO-PY-D1</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Analista de Inventario</t>
+          <t>Analista de Proyectos</t>
         </is>
       </c>
       <c r="I45" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J45" s="4" t="inlineStr"/>
     </row>
@@ -3017,41 +3011,45 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE PROYECTOS</t>
+          <t>ANALISTA DE SUPPLY CHAIN</t>
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>4600 PROYECTOS</t>
+          <t>4300 PLANTABAL SCH / 4400 PLANTABAL PURCHASE</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
+          <t>Quevedo / Samborondon</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PY-D1</t>
+          <t>GE-SO-PO-D1 / GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Analista de Proyectos</t>
+          <t>Analista Supply Chain / Analista de Supply Chain</t>
         </is>
       </c>
       <c r="I46" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="J46" s="5" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Evaluado en más de una matriz</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -3061,43 +3059,35 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE SUPPLY CHAIN</t>
+          <t>APRENDIZ</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>4300 PLANTABAL SCH / 4400 PLANTABAL PURCHASE</t>
+          <t>3801 PLANTABAL MANTENANCE #1</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Quevedo / Samborondon</t>
-        </is>
-      </c>
-      <c r="F47" s="13" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-PO-D1 / GE-SO-SC-D1</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>Analista Supply Chain / Analista de Supply Chain</t>
-        </is>
-      </c>
+          <t>Quevedo</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr"/>
       <c r="I47" s="6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Evaluado en más de una matriz</t>
+          <t>Requiere elaboración de matriz IPERC</t>
         </is>
       </c>
     </row>
@@ -3109,15 +3099,15 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>APRENDIZ</t>
+          <t>AUXILIAR ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>3801 PLANTABAL MANTENANCE #1</t>
+          <t>3158 PROYECTO W / 3251 PLANTABAL D100 #1 / 4800 PLANTABAL OPERATIONS MNG STAFF / 4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3125,19 +3115,27 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr"/>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
+        </is>
+      </c>
       <c r="I48" s="9" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Requiere elaboración de matriz IPERC</t>
+          <t>Evaluado en más de una matriz</t>
         </is>
       </c>
     </row>
@@ -3149,15 +3147,15 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
+          <t>COORDINADOR DE SUPPLY CHAIN</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>3158 PROYECTO W / 3251 PLANTABAL D100 #1 / 4800 PLANTABAL OPERATIONS MNG STAFF / 4808 MAINTENANCE MNG STAFF / 5918 PGS</t>
+          <t>4300 PLANTABAL SCH</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -3165,29 +3163,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1 / GE-SO-RL-D35</t>
+          <t>GE-SO-PO-D1</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativo / Auxiliar administrativo</t>
+          <t>Coordinador de Supply Chain</t>
         </is>
       </c>
       <c r="I49" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada) | Evaluado en más de una matriz</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -3197,7 +3191,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>COORDINADOR DE SUPPLY CHAIN</t>
+          <t>DIRECTOR DE OPERACIONES</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
@@ -3205,7 +3199,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>4300 PLANTABAL SCH</t>
+          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3213,23 +3207,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1</t>
+          <t>GE-SO-RL-D35</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>Coordinador de Supply Chain</t>
+          <t>Director de Operaciones</t>
         </is>
       </c>
       <c r="I50" s="9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J50" s="5" t="inlineStr"/>
     </row>
@@ -3241,7 +3235,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>DIRECTOR DE OPERACIONES</t>
+          <t>GERENTE DE PRODUCCION</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
@@ -3257,7 +3251,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="F51" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3269,11 +3263,11 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Director de Operaciones</t>
+          <t>Gerente de Producción</t>
         </is>
       </c>
       <c r="I51" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J51" s="4" t="inlineStr"/>
     </row>
@@ -3285,7 +3279,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>GERENTE DE PRODUCCION</t>
+          <t>GERENTE JR DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
@@ -3293,7 +3287,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
+          <t>4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -3301,23 +3295,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-RL-D35</t>
+          <t>GE-SO-MA-D1</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>Gerente de Producción</t>
+          <t>Gerente JR de mantenimiento</t>
         </is>
       </c>
       <c r="I52" s="9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J52" s="5" t="inlineStr"/>
     </row>
@@ -3329,7 +3323,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>GERENTE JR DE MANTENIMIENTO</t>
+          <t>INGENIERO DE PROYECTOS</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
@@ -3337,7 +3331,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>4808 MAINTENANCE MNG STAFF</t>
+          <t>4600 PROYECTOS</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -3345,23 +3339,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F53" s="13" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-PY-D1</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Gerente JR de mantenimiento</t>
+          <t>Ingeniero de Proyectos</t>
         </is>
       </c>
       <c r="I53" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J53" s="4" t="inlineStr"/>
     </row>
@@ -3373,7 +3367,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>INGENIERO DE PROYECTOS</t>
+          <t>JEFE DE BODEGA</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
@@ -3381,7 +3375,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>4600 PROYECTOS</t>
+          <t>2500 SERVICE CENTER</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -3389,25 +3383,21 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-PY-D1</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>Ingeniero de Proyectos</t>
-        </is>
-      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="J54" s="5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -3417,7 +3407,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE BODEGA</t>
+          <t>JEFE DE COMPRAS E IMPORTACIONES</t>
         </is>
       </c>
       <c r="C55" s="6" t="n">
@@ -3425,7 +3415,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>2500 SERVICE CENTER</t>
+          <t>4400 PLANTABAL PURCHASE</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -3433,19 +3423,27 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F55" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr"/>
-      <c r="H55" s="4" t="inlineStr"/>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-SC-D1</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Jefe de Compras</t>
+        </is>
+      </c>
       <c r="I55" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Requiere elaboración de matriz IPERC</t>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3455,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE COMPRAS E IMPORTACIONES</t>
+          <t>JEFE DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
@@ -3465,7 +3463,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>4400 PLANTABAL PURCHASE</t>
+          <t>4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -3473,29 +3471,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="F56" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SC-D1</t>
+          <t>GE-SO-MA-D1</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>Jefe de Compras</t>
+          <t>Jefe de mantenimiento</t>
         </is>
       </c>
       <c r="I56" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -3505,7 +3499,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE MANTENIMIENTO</t>
+          <t>JEFE DE PLANIFICACION Y LOGISTICA</t>
         </is>
       </c>
       <c r="C57" s="6" t="n">
@@ -3513,7 +3507,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>4808 MAINTENANCE MNG STAFF</t>
+          <t>4300 PLANTABAL SCH</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -3521,23 +3515,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F57" s="13" t="inlineStr">
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-PO-D1</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Jefe de mantenimiento</t>
+          <t>Jefe de Planificación y Logística</t>
         </is>
       </c>
       <c r="I57" s="6" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="J57" s="4" t="inlineStr"/>
     </row>
@@ -3549,7 +3543,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE PLANIFICACION Y LOGISTICA</t>
+          <t>JEFE DE PRODUCCION</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
@@ -3557,7 +3551,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>4300 PLANTABAL SCH</t>
+          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -3565,25 +3559,21 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-PO-D1</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>Jefe de Planificación y Logística</t>
-        </is>
-      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="J58" s="5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -3593,7 +3583,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE PRODUCCION</t>
+          <t>JEFE DE PROYECTOS</t>
         </is>
       </c>
       <c r="C59" s="6" t="n">
@@ -3601,7 +3591,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
+          <t>4600 PROYECTOS</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -3609,21 +3599,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F59" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr"/>
-      <c r="H59" s="4" t="inlineStr"/>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-PY-D1</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Jefe de Proyectos</t>
+        </is>
+      </c>
       <c r="I59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -3633,7 +3627,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE PROYECTOS</t>
+          <t>PLANIFICADOR DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
@@ -3641,7 +3635,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>4600 PROYECTOS</t>
+          <t>4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -3649,23 +3643,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr">
+      <c r="F60" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PY-D1</t>
+          <t>GE-SO-MA-D1</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>Jefe de Proyectos</t>
+          <t>Planificador de mantenimiento</t>
         </is>
       </c>
       <c r="I60" s="9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J60" s="5" t="inlineStr"/>
     </row>
@@ -3677,7 +3671,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>PLANIFICADOR DE MANTENIMIENTO</t>
+          <t>PROGRAMADOR DE PRODUCCCION</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
@@ -3685,7 +3679,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>4808 MAINTENANCE MNG STAFF</t>
+          <t>4300 PLANTABAL SCH</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -3693,23 +3687,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F61" s="13" t="inlineStr">
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-PO-D1</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Planificador de mantenimiento</t>
+          <t>Programador de Producción</t>
         </is>
       </c>
       <c r="I61" s="6" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J61" s="4" t="inlineStr"/>
     </row>
@@ -3721,15 +3715,15 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>PROGRAMADOR DE PRODUCCCION</t>
+          <t>SUPERVISOR DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>4300 PLANTABAL SCH</t>
+          <t>4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -3737,23 +3731,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F62" s="12" t="inlineStr">
+      <c r="F62" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1</t>
+          <t>GE-SO-MA-D1</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>Programador de Producción</t>
+          <t>Supervisor de mantenimiento</t>
         </is>
       </c>
       <c r="I62" s="9" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="J62" s="5" t="inlineStr"/>
     </row>
@@ -3765,15 +3759,15 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE MANTENIMIENTO</t>
+          <t>SUPERVISOR DE PRODUCCIÓN</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>4808 MAINTENANCE MNG STAFF</t>
+          <t>3010 KITS PRODUCTION - PGS / 3821 SUP DE PRODUCCION</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3781,25 +3775,21 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F63" s="13" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-MA-D1</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>Supervisor de mantenimiento</t>
-        </is>
-      </c>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr"/>
       <c r="I63" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -3809,15 +3799,15 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE PRODUCCIÓN</t>
+          <t>TECNICO DE INVENTARIO</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>3010 KITS PRODUCTION - PGS / 3821 SUP DE PRODUCCION</t>
+          <t>4950 INVENTARY</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -3825,39 +3815,43 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F64" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr"/>
-      <c r="H64" s="5" t="inlineStr"/>
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-CI-D1</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Técnico de Inventario</t>
+        </is>
+      </c>
       <c r="I64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Operaciones</t>
+          <t>QSE &amp; Operational Excellence</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>TECNICO DE INVENTARIO</t>
+          <t>ANALISTA DE CALIDAD</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>4950 INVENTARY</t>
+          <t>4500 PLANTABAL QUALITY</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3865,23 +3859,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F65" s="13" t="inlineStr">
+      <c r="F65" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-CI-D1</t>
+          <t>GE-SO-CC-D1</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Técnico de Inventario</t>
+          <t>Analista de calidad</t>
         </is>
       </c>
       <c r="I65" s="6" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="J65" s="4" t="inlineStr"/>
     </row>
@@ -3893,11 +3887,11 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE CALIDAD</t>
+          <t>COORDINADOR DE CALIDAD</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
@@ -3909,7 +3903,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F66" s="12" t="inlineStr">
+      <c r="F66" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3921,7 +3915,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>Analista de calidad</t>
+          <t>Coordinador de calidad</t>
         </is>
       </c>
       <c r="I66" s="9" t="n">
@@ -3937,15 +3931,15 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR DE CALIDAD</t>
+          <t>COORDINADOR DE EXCELENCIA OPERACIONAL</t>
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>4500 PLANTABAL QUALITY</t>
+          <t>4650 EXCELENCIA OPERACIONAL</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3953,23 +3947,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F67" s="13" t="inlineStr">
+      <c r="F67" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-CC-D1</t>
+          <t>GE-SO-EO-D1</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Coordinador de calidad</t>
+          <t>Coordinador de Excelencia Operacional</t>
         </is>
       </c>
       <c r="I67" s="6" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="J67" s="4" t="inlineStr"/>
     </row>
@@ -3981,15 +3975,15 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>COORDINADOR DE EXCELENCIA OPERACIONAL</t>
+          <t>COORDINADORA DE CERTIFICACIONES</t>
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>4650 EXCELENCIA OPERACIONAL</t>
+          <t>4350 CERTIFICACION FSC</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -3997,23 +3991,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F68" s="12" t="inlineStr">
+      <c r="F68" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-EO-D1</t>
+          <t>GE-SO-CE-D1</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>Coordinador de Excelencia Operacional</t>
+          <t>Coordinador/a de Certificaciones</t>
         </is>
       </c>
       <c r="I68" s="9" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J68" s="5" t="inlineStr"/>
     </row>
@@ -4025,7 +4019,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>COORDINADORA DE CERTIFICACIONES</t>
+          <t>ESPECIALISTA DE CERTIFICACIONES</t>
         </is>
       </c>
       <c r="C69" s="6" t="n">
@@ -4041,7 +4035,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F69" s="13" t="inlineStr">
+      <c r="F69" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -4053,11 +4047,11 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Coordinador/a de Certificaciones</t>
+          <t>Especialista de Certificaciones</t>
         </is>
       </c>
       <c r="I69" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J69" s="4" t="inlineStr"/>
     </row>
@@ -4069,7 +4063,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>ESPECIALISTA DE CERTIFICACIONES</t>
+          <t>GERENTE DE CALIDAD Y CERTIFICACIONES</t>
         </is>
       </c>
       <c r="C70" s="9" t="n">
@@ -4077,7 +4071,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>4350 CERTIFICACION FSC</t>
+          <t>4500 PLANTABAL QUALITY</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -4085,25 +4079,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F70" s="12" t="inlineStr">
+      <c r="F70" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-CE-D1</t>
+          <t>GE-SO-CC-D1</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>Especialista de Certificaciones</t>
+          <t>QSE &amp; Operational Excellence Manager</t>
         </is>
       </c>
       <c r="I70" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="J70" s="5" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -4113,15 +4111,15 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>GERENTE DE CALIDAD Y CERTIFICACIONES</t>
+          <t>INGENIERO DE SEGURIDAD  Y AMBIENTE</t>
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>4500 PLANTABAL QUALITY</t>
+          <t>4203 SEGURIDAD OCUPACIONAL Y AMBIENTE</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -4129,29 +4127,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F71" s="13" t="inlineStr">
+      <c r="F71" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-CC-D1</t>
+          <t>GE-SO-EHS-D1</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>QSE &amp; Operational Excellence Manager</t>
+          <t>Ingeniero de seguridad y ambiente</t>
         </is>
       </c>
       <c r="I71" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -4161,15 +4155,15 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>INGENIERO DE SEGURIDAD  Y AMBIENTE</t>
+          <t>TECNICO DE CALIDAD</t>
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>4203 SEGURIDAD OCUPACIONAL Y AMBIENTE</t>
+          <t>4500 PLANTABAL QUALITY</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -4177,23 +4171,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F72" s="12" t="inlineStr">
+      <c r="F72" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-EHS-D1</t>
+          <t>GE-SO-CC-D1</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>Ingeniero de seguridad y ambiente</t>
+          <t>Técnico de calidad</t>
         </is>
       </c>
       <c r="I72" s="9" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="J72" s="5" t="inlineStr"/>
     </row>
@@ -4205,15 +4199,15 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>TECNICO DE CALIDAD</t>
+          <t>TECNICO DE CERTIFICACIONES</t>
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>4500 PLANTABAL QUALITY / 4507 QUALITY SD</t>
+          <t>4350 CERTIFICACION FSC</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -4221,23 +4215,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F73" s="13" t="inlineStr">
+      <c r="F73" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-CC-D1</t>
+          <t>GE-SO-CE-D1</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Técnico de calidad</t>
+          <t>Técnico de Certificaciones</t>
         </is>
       </c>
       <c r="I73" s="6" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="J73" s="4" t="inlineStr"/>
     </row>
@@ -4249,15 +4243,15 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>TECNICO DE CERTIFICACIONES</t>
+          <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>4350 CERTIFICACION FSC</t>
+          <t>4203 SEGURIDAD OCUPACIONAL Y AMBIENTE</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -4265,72 +4259,28 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F74" s="12" t="inlineStr">
+      <c r="F74" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-CE-D1</t>
+          <t>GE-SO-EHS-D1</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>Técnico de Certificaciones</t>
+          <t>Tecnico de seguridad y ambiente</t>
         </is>
       </c>
       <c r="I74" s="9" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J74" s="5" t="inlineStr"/>
     </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>QSE &amp; Operational Excellence</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>4203 SEGURIDAD OCUPACIONAL Y AMBIENTE</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F75" s="13" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-EHS-D1</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>Tecnico de seguridad y ambiente</t>
-        </is>
-      </c>
-      <c r="I75" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:J75"/>
+  <autoFilter ref="A4:J74"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -4345,7 +4295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4449,12 +4399,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>COORDINADOR DE SEGURIDAD FISICA</t>
+          <t>CHOFER</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
@@ -4462,12 +4412,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1200 PLANTATION MANAGEMENT</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -4486,7 +4436,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>CHOFER</t>
+          <t>GERENTE GENERAL</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -4494,7 +4444,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -4513,12 +4463,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>GERENTE GENERAL</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
@@ -4526,12 +4476,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
+          <t>5930 3ACM Expenses</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -4545,12 +4495,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>ANALISTA DE IMPUESTOS</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
@@ -4563,7 +4513,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>5930 3ACM Expenses</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -4582,7 +4532,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>ANALISTA DE IMPUESTOS</t>
+          <t>ANALISTA DE REDES</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -4595,7 +4545,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -4742,7 +4692,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>SENIOR BUSINESS CONTROLLER</t>
+          <t>MENSAJERO / REPARTIDOR</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
@@ -4755,7 +4705,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -4769,12 +4719,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Operaciones</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>APRENDIZ</t>
+          <t>SENIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -4782,12 +4732,12 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>3801 PLANTABAL MANTENANCE #1</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -4806,7 +4756,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>JEFE DE BODEGA</t>
+          <t>APRENDIZ</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
@@ -4819,7 +4769,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2500 SERVICE CENTER</t>
+          <t>3801 PLANTABAL MANTENANCE #1</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -4838,7 +4788,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>JEFE DE PRODUCCION</t>
+          <t>JEFE DE BODEGA</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
@@ -4851,7 +4801,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
+          <t>2500 SERVICE CENTER</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -4862,8 +4812,40 @@
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Operaciones</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>JEFE DE PRODUCCION</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Quevedo</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Elaborar matriz IPERC para el puesto</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:H18"/>
+  <autoFilter ref="A4:H19"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
@@ -4878,7 +4860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5060,12 +5042,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>ENFERMERO OCUPACIONAL</t>
+          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ENFERMERA/O</t>
+          <t>AUXILIAR ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -5080,7 +5062,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Misma funcion, denominacion en masculino/ocupacional</t>
+          <t>En el head count consta como AUXILIAR ADMINISTRATIVO. La denominacion 'Auxiliar de servicios de salud' se uso solo a efectos de la matriz de Salud Ocupacional. Corresponde al auxiliar administrativo asignado a ADM-L&amp;RH (1 persona); los 5 de Operaciones estan cubiertos por GE-SO-MA-D1.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -5092,22 +5074,22 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-IT-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>GERENTE TECNOLOGICO</t>
+          <t>ENFERMERO OCUPACIONAL</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>REGIONAL IT  MANAGER</t>
+          <t>ENFERMERA/O</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -5117,7 +5099,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Mismo puesto, denominacion distinta</t>
+          <t>Misma funcion, denominacion en masculino/ocupacional</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -5129,22 +5111,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PGS-D1</t>
+          <t>GE-SO-IT-D1</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>INGENIERO DE DISENO E INGENIERIA</t>
+          <t>GERENTE TECNOLOGICO</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>INGENIERO DE DISEÑO</t>
+          <t>REGIONAL IT  MANAGER</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Engicore</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -5154,7 +5136,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Mismo puesto</t>
+          <t>Mismo puesto, denominacion distinta</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -5166,22 +5148,22 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-SC-D1</t>
+          <t>GE-SO-PGS-D1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE COMPRAS</t>
+          <t>INGENIERO DE DISENO E INGENIERIA</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE COMPRAS E IMPORTACIONES</t>
+          <t>INGENIERO DE DISEÑO</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Operaciones</t>
+          <t>Engicore</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -5191,7 +5173,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Mismo puesto, confirmado por Hector</t>
+          <t>Mismo puesto</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -5203,22 +5185,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>MEDICO OCUPACIONAL</t>
+          <t>JEFE DE COMPRAS</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>MEDICO</t>
+          <t>JEFE DE COMPRAS E IMPORTACIONES</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -5228,7 +5210,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>El head count de octubre 2026 renombro el cargo de MEDICO OCUPACIONAL a MEDICO</t>
+          <t>Mismo puesto, confirmado por Hector</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -5277,182 +5259,145 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
+          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
+          <t>(no consta)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Regularizado - cerrado</t>
+          <t>Cargo nuevo no registrado</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>REGULARIZADO - consta en el head count de octubre 2026 con la misma denominacion de la matriz</t>
+          <t>ANALIZADO en matriz / NO CONSTA en head count V1.1</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Ninguna. Accion correctiva cumplida.</t>
+          <t>Incorporar el cargo a la base de head count</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-TH-D1</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
+          <t>PEOPLE OPERATIONS PARTNER</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
+          <t>(no consta)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Regularizado - cerrado</t>
+          <t>Cargo nuevo no registrado</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>REGULARIZADO - consta en el head count de octubre 2026</t>
+          <t>ANALIZADO en matriz / NO CONSTA en head count V1.1</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Ninguna. Accion correctiva cumplida.</t>
+          <t>Incorporar el cargo a la base de head count</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>PEOPLE OPERATIONS PARTNER</t>
+          <t>COORDINADOR DE TESORERIA</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>PEOPLE OPERATIONS PARTNER</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>ADM-L&amp;RH</t>
-        </is>
-      </c>
+          <t>(no existe)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Regularizado - cerrado</t>
+          <t>Cargo obsoleto</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>REGULARIZADO - consta en el head count de octubre 2026</t>
+          <t>CARGO INEXISTENTE - suprimido de la estructura</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Ninguna. Accion correctiva cumplida.</t>
+          <t>ELIMINAR el bloque completo de la matriz GE-SO-FI-D1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-RL-D35</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR DE TESORERIA</t>
+          <t>Jefe de Producción (MV y Secado)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>(no existe)</t>
+          <t>(no consta)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Cargo obsoleto</t>
+          <t>SIN CLASIFICAR - detectado este mes</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>CARGO INEXISTENTE - suprimido de la estructura</t>
+          <t>Puesto evaluado en la matriz que no aparece en el head count del mes</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>ELIMINAR el bloque completo de la matriz GE-SO-FI-D1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-RL-D35</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Jefe de Producción (MV y Secado)</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>(no consta)</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>SIN CLASIFICAR - detectado este mes</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Puesto evaluado en la matriz que no aparece en el head count del mes</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
           <t>Definir si es cargo nuevo, denominación alterna o cargo suprimido</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G18"/>
+  <autoFilter ref="A4:G17"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -6024,409 +5969,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CAMBIOS RESPECTO AL CORTE ANTERIOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tipo de cambio</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Área</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Cargo</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>N° personas</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Estado de cobertura</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Acción sugerida</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>ALTA - cargo nuevo</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ADM-L&amp;RH</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verificar cobertura</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>ALTA - cargo nuevo</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>ADM-L&amp;RH</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>COORDINADOR DE SEGURIDAD FISICA</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Verificar cobertura</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>ALTA - cargo nuevo</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>ADM-L&amp;RH</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>MEDICO</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verificar cobertura</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>ALTA - cargo nuevo</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>ADM-L&amp;RH</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>PEOPLE OPERATIONS PARTNER</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Verificar cobertura</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>VARIACIÓN de dotación (2 → 1)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>IT&amp;FIN</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>COORDINADOR CONTABLE</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Sin acción si el cargo ya está cubierto</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>ALTA - cargo nuevo</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>IT&amp;FIN</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Verificar cobertura</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>VARIACIÓN de dotación (3 → 2)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Operaciones</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>TECNICO DE INVENTARIO</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Sin acción si el cargo ya está cubierto</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>VARIACIÓN de dotación (4 → 3)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>QSE &amp; Operational Excellence</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>TECNICO DE CALIDAD</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Sin acción si el cargo ya está cubierto</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>BAJA - cargo ya no consta</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>ADM-L&amp;RH</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>BAJA - cargo ya no consta</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>ADM-L&amp;RH</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>MÉDICO OCUPACIONAL</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>BAJA - cargo ya no consta</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>IT&amp;FIN</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>ANALISTA DE REDES</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>BAJA - cargo ya no consta</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>IT&amp;FIN</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>MENSAJERO / REPARTIDOR</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:F16"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Cobertura_IPERC_Administrativos_CAR.xlsx
+++ b/Cobertura_IPERC_Administrativos_CAR.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Alcance y criterios'!$A$4:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Resumen por área'!$A$4:$I$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Matriz consolidada'!$A$4:$J$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$H$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Observaciones'!$A$4:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Trazabilidad'!$A$4:$F$22</definedName>
   </definedNames>
@@ -872,22 +872,22 @@
         <v>22</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>37</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -1103,22 +1103,22 @@
         <v>70</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F13" s="15" t="n">
         <v>101</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I13" s="14" t="inlineStr"/>
     </row>
@@ -3559,19 +3559,27 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="5" t="inlineStr"/>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-RL-D35</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Jefe de Producción (MV y Secado)</t>
+        </is>
+      </c>
       <c r="I58" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Requiere elaboración de matriz IPERC</t>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4812,40 +4820,8 @@
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Operaciones</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>JEFE DE PRODUCCION</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Elaborar matriz IPERC para el puesto</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:H19"/>
+  <autoFilter ref="A4:H18"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
@@ -5222,22 +5198,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-CC-D1</t>
+          <t>GE-SO-RL-D35</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>QSE &amp; OPERATIONAL EXCELLENCE MANAGER</t>
+          <t>JEFE DE PRODUCCION (MV Y SECADO)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>GERENTE DE CALIDAD Y CERTIFICACIONES</t>
+          <t>JEFE DE PRODUCCION</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>QSE &amp; Operational Excellence</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -5247,7 +5223,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Mismo puesto, distinta denominacion entre matriz y head count</t>
+          <t>Mismo puesto, confirmado por Hector. La matriz precisa entre parentesis las lineas que atiende (MV y Secado)</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -5259,49 +5235,49 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-CC-D1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
+          <t>QSE &amp; OPERATIONAL EXCELLENCE MANAGER</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>(no consta)</t>
+          <t>GERENTE DE CALIDAD Y CERTIFICACIONES</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>QSE &amp; Operational Excellence</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Cargo nuevo no registrado</t>
+          <t>Equivalencia de denominación</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>ANALIZADO en matriz / NO CONSTA en head count V1.1</t>
+          <t>Mismo puesto, distinta denominacion entre matriz y head count</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Incorporar el cargo a la base de head count</t>
+          <t>Unificar la denominación en la matriz según el head count</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>PEOPLE OPERATIONS PARTNER</t>
+          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -5311,7 +5287,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -5333,66 +5309,70 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-TH-D1</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>COORDINADOR DE TESORERIA</t>
+          <t>PEOPLE OPERATIONS PARTNER</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>(no existe)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr"/>
+          <t>(no consta)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Cargo obsoleto</t>
+          <t>Cargo nuevo no registrado</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>CARGO INEXISTENTE - suprimido de la estructura</t>
+          <t>ANALIZADO en matriz / NO CONSTA en head count V1.1</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>ELIMINAR el bloque completo de la matriz GE-SO-FI-D1</t>
+          <t>Incorporar el cargo a la base de head count</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-RL-D35</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Producción (MV y Secado)</t>
+          <t>COORDINADOR DE TESORERIA</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>(no consta)</t>
+          <t>(no existe)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>SIN CLASIFICAR - detectado este mes</t>
+          <t>Cargo obsoleto</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Puesto evaluado en la matriz que no aparece en el head count del mes</t>
+          <t>CARGO INEXISTENTE - suprimido de la estructura</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Definir si es cargo nuevo, denominación alterna o cargo suprimido</t>
+          <t>ELIMINAR el bloque completo de la matriz GE-SO-FI-D1</t>
         </is>
       </c>
     </row>

--- a/Cobertura_IPERC_Administrativos_CAR.xlsx
+++ b/Cobertura_IPERC_Administrativos_CAR.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Resumen por área'!$A$4:$I$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Matriz consolidada'!$A$4:$J$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Observaciones'!$A$4:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Observaciones'!$A$4:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Trazabilidad'!$A$4:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -564,7 +564,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4858,7 +4858,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
+          <t>AUXILIAR DE SERVICIOS DE SALUD / AUXILIAR ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>En el head count consta como AUXILIAR ADMINISTRATIVO. La denominacion 'Auxiliar de servicios de salud' se uso solo a efectos de la matriz de Salud Ocupacional. Corresponde al auxiliar administrativo asignado a ADM-L&amp;RH (1 persona); los 5 de Operaciones estan cubiertos por GE-SO-MA-D1.</t>
+          <t>El head count de octubre 2026 adopto la denominacion de la matriz; antes constaba como AUXILIAR ADMINISTRATIVO. Se aceptan ambas.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -5235,22 +5235,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-CC-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>QSE &amp; OPERATIONAL EXCELLENCE MANAGER</t>
+          <t>MEDICO OCUPACIONAL</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>GERENTE DE CALIDAD Y CERTIFICACIONES</t>
+          <t>MEDICO OCUPACIONAL / MEDICO</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>QSE &amp; Operational Excellence</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Mismo puesto, distinta denominacion entre matriz y head count</t>
+          <t>El head count de octubre 2026 renombro el cargo de MEDICO OCUPACIONAL a MEDICO. Se aceptan ambas denominaciones.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -5272,49 +5272,49 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-CC-D1</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
+          <t>QSE &amp; OPERATIONAL EXCELLENCE MANAGER</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>(no consta)</t>
+          <t>GERENTE DE CALIDAD Y CERTIFICACIONES</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>QSE &amp; Operational Excellence</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Cargo nuevo no registrado</t>
+          <t>Equivalencia de denominación</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>ANALIZADO en matriz / NO CONSTA en head count V1.1</t>
+          <t>Mismo puesto, distinta denominacion entre matriz y head count</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Incorporar el cargo a la base de head count</t>
+          <t>Unificar la denominación en la matriz según el head count</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>PEOPLE OPERATIONS PARTNER</t>
+          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -5346,38 +5346,75 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>GE-SO-TH-D1</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>PEOPLE OPERATIONS PARTNER</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>(no consta)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Cargo nuevo no registrado</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>ANALIZADO en matriz / NO CONSTA en head count V1.1</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Incorporar el cargo a la base de head count</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t>GE-SO-FI-D1</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>COORDINADOR DE TESORERIA</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>(no existe)</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Cargo obsoleto</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>CARGO INEXISTENTE - suprimido de la estructura</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>ELIMINAR el bloque completo de la matriz GE-SO-FI-D1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G17"/>
+  <autoFilter ref="A4:G18"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -5413,7 +5450,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 06/10/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
         </is>
       </c>
     </row>

--- a/Cobertura_IPERC_Administrativos_CAR.xlsx
+++ b/Cobertura_IPERC_Administrativos_CAR.xlsx
@@ -13,14 +13,16 @@
     <sheet name="4. Brechas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5. Observaciones" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="6. Trazabilidad" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7. Cambios del mes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Alcance y criterios'!$A$4:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Resumen por área'!$A$4:$I$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Matriz consolidada'!$A$4:$J$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Observaciones'!$A$4:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Matriz consolidada'!$A$4:$J$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Observaciones'!$A$4:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Trazabilidad'!$A$4:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'7. Cambios del mes'!$A$4:$F$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -163,10 +165,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -836,25 +838,25 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>10</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -881,10 +883,10 @@
         <v>86</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>9</v>
@@ -931,26 +933,26 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>1</v>
@@ -964,33 +966,33 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="7" t="n">
-        <v>100</v>
-      </c>
       <c r="F9" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>CONFORME</t>
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>CON BRECHAS</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1023,7 @@
       <c r="H10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
@@ -1054,7 +1056,7 @@
       <c r="H11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
@@ -1079,15 +1081,15 @@
         <v>100</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
@@ -1100,25 +1102,25 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="G13" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="F13" s="15" t="n">
-        <v>101</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>81</v>
-      </c>
       <c r="H13" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I13" s="14" t="inlineStr"/>
     </row>
@@ -1138,7 +1140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1243,7 +1245,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1287,7 +1289,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1331,7 +1333,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1375,7 +1377,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1419,7 +1421,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1447,7 +1449,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
+          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -1463,29 +1465,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
+          <t>Auxiliar de servicios de salud</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Evaluado en más de una matriz</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1511,7 +1509,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1555,7 +1553,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1583,7 +1581,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
+          <t>COORDINADOR DE SEGURIDAD FISICA</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
@@ -1591,7 +1589,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>5500 HR</t>
+          <t>1200 PLANTATION MANAGEMENT</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1599,25 +1597,21 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-TH-D1</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
-        </is>
-      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1627,15 +1621,15 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>ENFERMERA/O</t>
+          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>4201 SALUD OCUPACIONAL</t>
+          <t>5500 HR</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1643,29 +1637,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-TH-D1</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Enfermero Ocupacional</t>
+          <t>COORDINADORA DE DESARROLLO ORGANIZACIONAL</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1675,15 +1665,15 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>HR BUSINESS PARTNER AMERICAS</t>
+          <t>ENFERMERA/O</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>5500 HR</t>
+          <t>4201 SALUD OCUPACIONAL</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1691,25 +1681,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>HR BUSINNES PARTNER AMERICAS</t>
+          <t>Enfermero Ocupacional</t>
         </is>
       </c>
       <c r="I15" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1719,7 +1713,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>HR DIRECTOR AMERICAS</t>
+          <t>HR BUSINESS PARTNER AMERICAS</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -1727,7 +1721,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>5700 ADMINISTRACION</t>
+          <t>5500 HR</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1735,7 +1729,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -1747,11 +1741,11 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>HR DIRECTOR AMERICAS</t>
+          <t>HR BUSINNES PARTNER AMERICAS</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J16" s="5" t="inlineStr"/>
     </row>
@@ -1763,15 +1757,15 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>INGENIERO DE SEGURIDAD  Y AMBIENTE</t>
+          <t>HR DIRECTOR AMERICAS</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>4101 PLANTABAL MANUFACTURING #1</t>
+          <t>5700 ADMINISTRACION</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1779,23 +1773,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-EHS-D1</t>
+          <t>GE-SO-TH-D1</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Ingeniero de seguridad y ambiente</t>
+          <t>HR DIRECTOR AMERICAS</t>
         </is>
       </c>
       <c r="I17" s="6" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
     </row>
@@ -1807,15 +1801,15 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>MÉDICO OCUPACIONAL</t>
+          <t>INGENIERO DE SEGURIDAD  Y AMBIENTE</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>4201 SALUD OCUPACIONAL</t>
+          <t>4101 PLANTABAL MANUFACTURING #1</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1823,23 +1817,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-EHS-D1</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Medico Ocupacional</t>
+          <t>Ingeniero de seguridad y ambiente</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J18" s="5" t="inlineStr"/>
     </row>
@@ -1851,7 +1845,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
+          <t>MEDICO</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
@@ -1859,7 +1853,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>4101 PLANTABAL MANUFACTURING #1</t>
+          <t>4201 SALUD OCUPACIONAL</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1867,35 +1861,39 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-EHS-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Tecnico de seguridad y ambiente</t>
+          <t>Medico Ocupacional</t>
         </is>
       </c>
       <c r="I19" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>ESG/Lab</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE LABORATORIO</t>
+          <t>PEOPLE OPERATIONS PARTNER</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
@@ -1903,7 +1901,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>5210 LABORATORIO DE BALSA</t>
+          <t>5500 HR</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1911,35 +1909,35 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-BL-D1</t>
+          <t>GE-SO-TH-D1</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Supervisor de Laboratorio</t>
+          <t>PEOPLE OPERATIONS PARTNER</t>
         </is>
       </c>
       <c r="I20" s="9" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="J20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>ESG/Lab</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>TECNICO DE LABORATORIO</t>
+          <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
@@ -1947,7 +1945,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>5210 LABORATORIO DE BALSA</t>
+          <t>4101 PLANTABAL MANUFACTURING #1</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1955,43 +1953,43 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-BL-D1</t>
+          <t>GE-SO-EHS-D1</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Técnico de Laboratorio</t>
+          <t>Tecnico de seguridad y ambiente</t>
         </is>
       </c>
       <c r="I21" s="6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Engicore</t>
+          <t>ESG/Lab</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE DISEÑO E INGENIERIA</t>
+          <t>SUPERVISOR DE LABORATORIO</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>4011 DISEÑO E INGENIERIA-PGS</t>
+          <t>5210 LABORATORIO DE BALSA</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -1999,19 +1997,19 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PGS-D1</t>
+          <t>GE-SO-BL-D1</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Analista de Diseño e Ingenieria</t>
+          <t>Supervisor de Laboratorio</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -2022,12 +2020,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Engicore</t>
+          <t>ESG/Lab</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>INGENIERO DE DISEÑO</t>
+          <t>TECNICO DE LABORATORIO</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
@@ -2035,7 +2033,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>4011 DISEÑO E INGENIERIA-PGS</t>
+          <t>5210 LABORATORIO DE BALSA</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2043,29 +2041,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PGS-D1</t>
+          <t>GE-SO-BL-D1</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Ingeniero de Diseño e Ingenieria</t>
+          <t>Técnico de Laboratorio</t>
         </is>
       </c>
       <c r="I23" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2075,15 +2069,15 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE DISEÑO E INGENIERIA</t>
+          <t>ANALISTA DE DISEÑO E INGENIERIA</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>5006 PGS-ENGICORE AMERICAS</t>
+          <t>4011 DISEÑO E INGENIERIA-PGS</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2091,7 +2085,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2103,7 +2097,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Jefe de Diseño e Ingenieria</t>
+          <t>Analista de Diseño e Ingenieria</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -2114,12 +2108,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>Engicore</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CHOFER</t>
+          <t>INGENIERO DE DISEÑO</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
@@ -2127,39 +2121,47 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
+          <t>4011 DISEÑO E INGENIERIA-PGS</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Samborondon</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr"/>
+          <t>Quevedo</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-PGS-D1</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Ingeniero de Diseño e Ingenieria</t>
+        </is>
+      </c>
       <c r="I25" s="6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Requiere elaboración de matriz IPERC</t>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>Engicore</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>GERENTE GENERAL</t>
+          <t>JEFE DE DISEÑO E INGENIERIA</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
@@ -2167,7 +2169,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
+          <t>5006 PGS-ENGICORE AMERICAS</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2175,31 +2177,35 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-PGS-D1</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Jefe de Diseño e Ingenieria</t>
+        </is>
+      </c>
       <c r="I26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>CHOFER</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
@@ -2207,7 +2213,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5930 3ACM Expenses</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2234,12 +2240,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE IMPUESTOS</t>
+          <t>GERENTE GENERAL</t>
         </is>
       </c>
       <c r="C28" s="9" t="n">
@@ -2247,12 +2253,12 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
@@ -2274,12 +2280,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE REDES</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
@@ -2287,7 +2293,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5930 3ACM Expenses</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2319,7 +2325,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA FINANCIERO</t>
+          <t>ANALISTA DE IMPUESTOS</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
@@ -2335,25 +2341,21 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-FI-D1</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>Analista financiero</t>
-        </is>
-      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2363,7 +2365,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>ASISTENTE DE DESARROLLO DE SISTEMA</t>
+          <t>ANALISTA FINANCIERO</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -2371,7 +2373,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2379,29 +2381,25 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-IT-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Analista de desarrollo y sistema</t>
+          <t>Analista financiero</t>
         </is>
       </c>
       <c r="I31" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2411,15 +2409,15 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>COORDINADOR CONTABLE</t>
+          <t>ASISTENTE DE DESARROLLO DE SISTEMA</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2427,25 +2425,29 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-IT-D1</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Coordinador Contable</t>
+          <t>Analista de desarrollo y sistema</t>
         </is>
       </c>
       <c r="I32" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="5" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2455,11 +2457,11 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR CONTABLE Y DE IMPUESTOS</t>
+          <t>COORDINADOR CONTABLE</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
@@ -2471,7 +2473,7 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -2483,11 +2485,11 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Coordinador Contable y de Impuestos</t>
+          <t>Coordinador Contable</t>
         </is>
       </c>
       <c r="I33" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J33" s="4" t="inlineStr"/>
     </row>
@@ -2499,7 +2501,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>DESARROLLADOR JR</t>
+          <t>COORDINADOR CONTABLE Y DE IMPUESTOS</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
@@ -2507,7 +2509,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2515,23 +2517,23 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F34" s="13" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-IT-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>Desarrollador JR</t>
+          <t>Coordinador Contable y de Impuestos</t>
         </is>
       </c>
       <c r="I34" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J34" s="5" t="inlineStr"/>
     </row>
@@ -2543,15 +2545,15 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>DIRECTOR FINANCIERO</t>
+          <t>DESARROLLADOR JR</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -2559,21 +2561,25 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr"/>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-IT-D1</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Desarrollador JR</t>
+        </is>
+      </c>
       <c r="I35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -2583,7 +2589,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>GERENTE FINANCIERO</t>
+          <t>DIRECTOR FINANCIERO</t>
         </is>
       </c>
       <c r="C36" s="9" t="n">
@@ -2623,7 +2629,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>HELP DESK</t>
+          <t>GERENTE FINANCIERO</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
@@ -2631,33 +2637,29 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-IT-D1</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>Help Desk</t>
-        </is>
-      </c>
+          <t>Samborondon</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2667,7 +2669,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
+          <t>HELP DESK</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
@@ -2680,24 +2682,28 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
+          <t>Quevedo</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-IT-D1</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Help Desk</t>
+        </is>
+      </c>
       <c r="I38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -2707,7 +2713,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
@@ -2715,7 +2721,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -2747,7 +2753,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>MENSAJERO / REPARTIDOR</t>
+          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
@@ -2763,21 +2769,25 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-FI-D1</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Jefe de Contabilidad e Impuestos</t>
+        </is>
+      </c>
       <c r="I40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -2787,7 +2797,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>REGIONAL IT  MANAGER</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
@@ -2795,7 +2805,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -2803,27 +2813,19 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-IT-D1</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Gerente tecnologico</t>
-        </is>
-      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+          <t>Requiere elaboración de matriz IPERC</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2837,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>SENIOR BUSINESS CONTROLLER</t>
+          <t>REGIONAL IT  MANAGER</t>
         </is>
       </c>
       <c r="C42" s="9" t="n">
@@ -2843,7 +2845,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2851,31 +2853,39 @@
           <t>Samborondon</t>
         </is>
       </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr"/>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-IT-D1</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Gerente tecnologico</t>
+        </is>
+      </c>
       <c r="I42" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Requiere elaboración de matriz IPERC</t>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Operaciones</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE COMPRAS</t>
+          <t>SENIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
@@ -2883,35 +2893,27 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>4400 PLANTABAL PURCHASE</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-SC-D1</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>Analista Compras</t>
-        </is>
-      </c>
+          <t>Samborondon</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+          <t>Requiere elaboración de matriz IPERC</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2925,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE INVENTARIO</t>
+          <t>ANALISTA DE COMPRAS</t>
         </is>
       </c>
       <c r="C44" s="9" t="n">
@@ -2931,7 +2933,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>4950 INVENTARY</t>
+          <t>4400 PLANTABAL PURCHASE</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -2939,25 +2941,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F44" s="13" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-CI-D1</t>
+          <t>GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Analista de Inventario</t>
+          <t>Analista Compras</t>
         </is>
       </c>
       <c r="I44" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J44" s="5" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2967,7 +2973,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE PROYECTOS</t>
+          <t>ANALISTA DE INVENTARIO</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
@@ -2975,7 +2981,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>4600 PROYECTOS</t>
+          <t>4950 INVENTARY</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -2983,23 +2989,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F45" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PY-D1</t>
+          <t>GE-SO-CI-D1</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Analista de Proyectos</t>
+          <t>Analista de Inventario</t>
         </is>
       </c>
       <c r="I45" s="6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J45" s="4" t="inlineStr"/>
     </row>
@@ -3011,45 +3017,41 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>ANALISTA DE SUPPLY CHAIN</t>
+          <t>ANALISTA DE PROYECTOS</t>
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>4300 PLANTABAL SCH / 4400 PLANTABAL PURCHASE</t>
+          <t>4600 PROYECTOS</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Quevedo / Samborondon</t>
-        </is>
-      </c>
-      <c r="F46" s="13" t="inlineStr">
+          <t>Quevedo</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1 / GE-SO-SC-D1</t>
+          <t>GE-SO-PY-D1</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Analista Supply Chain / Analista de Supply Chain</t>
+          <t>Analista de Proyectos</t>
         </is>
       </c>
       <c r="I46" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>Evaluado en más de una matriz</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -3059,35 +3061,43 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>APRENDIZ</t>
+          <t>ANALISTA DE SUPPLY CHAIN</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3801 PLANTABAL MANTENANCE #1</t>
+          <t>4300 PLANTABAL SCH / 4400 PLANTABAL PURCHASE</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr"/>
-      <c r="H47" s="4" t="inlineStr"/>
+          <t>Quevedo / Samborondon</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-PO-D1 / GE-SO-SC-D1</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Analista Supply Chain / Analista de Supply Chain</t>
+        </is>
+      </c>
       <c r="I47" s="6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Requiere elaboración de matriz IPERC</t>
+          <t>Evaluado en más de una matriz</t>
         </is>
       </c>
     </row>
@@ -3099,15 +3109,15 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
+          <t>APRENDIZ</t>
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>3158 PROYECTO W / 3251 PLANTABAL D100 #1 / 4800 PLANTABAL OPERATIONS MNG STAFF / 4808 MAINTENANCE MNG STAFF</t>
+          <t>3801 PLANTABAL MANTENANCE #1</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3115,27 +3125,19 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
-        </is>
-      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="9" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Evaluado en más de una matriz</t>
+          <t>Requiere elaboración de matriz IPERC</t>
         </is>
       </c>
     </row>
@@ -3147,15 +3149,15 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR DE SUPPLY CHAIN</t>
+          <t>AUXILIAR ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>4300 PLANTABAL SCH</t>
+          <t>3158 PROYECTO W / 3251 PLANTABAL D100 #1 / 4800 PLANTABAL OPERATIONS MNG STAFF / 4808 MAINTENANCE MNG STAFF / 5918 PGS</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -3163,25 +3165,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="F49" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1</t>
+          <t>GE-SO-MA-D1 / GE-SO-RL-D35 / GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Coordinador de Supply Chain</t>
+          <t>Auxiliar Administrativo / Auxiliar administrativo / Auxiliar de servicios de salud</t>
         </is>
       </c>
       <c r="I49" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>Evaluado en más de una matriz</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -3191,7 +3197,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>DIRECTOR DE OPERACIONES</t>
+          <t>COORDINADOR DE SUPPLY CHAIN</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
@@ -3199,7 +3205,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
+          <t>4300 PLANTABAL SCH</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3207,23 +3213,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="F50" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-RL-D35</t>
+          <t>GE-SO-PO-D1</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>Director de Operaciones</t>
+          <t>Coordinador de Supply Chain</t>
         </is>
       </c>
       <c r="I50" s="9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J50" s="5" t="inlineStr"/>
     </row>
@@ -3235,7 +3241,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>GERENTE DE PRODUCCION</t>
+          <t>DIRECTOR DE OPERACIONES</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
@@ -3251,7 +3257,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="F51" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3263,11 +3269,11 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Gerente de Producción</t>
+          <t>Director de Operaciones</t>
         </is>
       </c>
       <c r="I51" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J51" s="4" t="inlineStr"/>
     </row>
@@ -3279,7 +3285,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>GERENTE JR DE MANTENIMIENTO</t>
+          <t>GERENTE DE PRODUCCION</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
@@ -3287,7 +3293,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>4808 MAINTENANCE MNG STAFF</t>
+          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -3295,23 +3301,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-RL-D35</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>Gerente JR de mantenimiento</t>
+          <t>Gerente de Producción</t>
         </is>
       </c>
       <c r="I52" s="9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J52" s="5" t="inlineStr"/>
     </row>
@@ -3323,7 +3329,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>INGENIERO DE PROYECTOS</t>
+          <t>GERENTE JR DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
@@ -3331,7 +3337,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>4600 PROYECTOS</t>
+          <t>4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -3339,23 +3345,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="F53" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PY-D1</t>
+          <t>GE-SO-MA-D1</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Ingeniero de Proyectos</t>
+          <t>Gerente JR de mantenimiento</t>
         </is>
       </c>
       <c r="I53" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J53" s="4" t="inlineStr"/>
     </row>
@@ -3367,7 +3373,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE BODEGA</t>
+          <t>INGENIERO DE PROYECTOS</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
@@ -3375,7 +3381,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>2500 SERVICE CENTER</t>
+          <t>4600 PROYECTOS</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -3383,21 +3389,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F54" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr"/>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-PY-D1</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Ingeniero de Proyectos</t>
+        </is>
+      </c>
       <c r="I54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -3407,7 +3417,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE COMPRAS E IMPORTACIONES</t>
+          <t>JEFE DE BODEGA</t>
         </is>
       </c>
       <c r="C55" s="6" t="n">
@@ -3415,7 +3425,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>4400 PLANTABAL PURCHASE</t>
+          <t>2500 SERVICE CENTER</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -3423,27 +3433,19 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>GE-SO-SC-D1</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>Jefe de Compras</t>
-        </is>
-      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
       <c r="I55" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+          <t>Requiere elaboración de matriz IPERC</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3457,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE MANTENIMIENTO</t>
+          <t>JEFE DE COMPRAS E IMPORTACIONES</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
@@ -3463,7 +3465,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>4808 MAINTENANCE MNG STAFF</t>
+          <t>4400 PLANTABAL PURCHASE</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -3471,25 +3473,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F56" s="13" t="inlineStr">
+      <c r="F56" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>Jefe de mantenimiento</t>
+          <t>Jefe de Compras</t>
         </is>
       </c>
       <c r="I56" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="J56" s="5" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -3499,7 +3505,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE PLANIFICACION Y LOGISTICA</t>
+          <t>JEFE DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C57" s="6" t="n">
@@ -3507,7 +3513,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>4300 PLANTABAL SCH</t>
+          <t>4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -3515,23 +3521,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="F57" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1</t>
+          <t>GE-SO-MA-D1</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Planificación y Logística</t>
+          <t>Jefe de mantenimiento</t>
         </is>
       </c>
       <c r="I57" s="6" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="J57" s="4" t="inlineStr"/>
     </row>
@@ -3543,7 +3549,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE PRODUCCION</t>
+          <t>JEFE DE PLANIFICACION Y LOGISTICA</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
@@ -3551,7 +3557,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
+          <t>4300 PLANTABAL SCH</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -3559,29 +3565,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F58" s="13" t="inlineStr">
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-RL-D35</t>
+          <t>GE-SO-PO-D1</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>Jefe de Producción (MV y Secado)</t>
+          <t>Jefe de Planificación y Logística</t>
         </is>
       </c>
       <c r="I58" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -3591,7 +3593,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>JEFE DE PROYECTOS</t>
+          <t>JEFE DE PRODUCCION</t>
         </is>
       </c>
       <c r="C59" s="6" t="n">
@@ -3599,7 +3601,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>4600 PROYECTOS</t>
+          <t>4800 PLANTABAL OPERATIONS MNG STAFF</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -3607,25 +3609,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F59" s="12" t="inlineStr">
+      <c r="F59" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PY-D1</t>
+          <t>GE-SO-RL-D35</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Proyectos</t>
+          <t>Jefe de Producción (MV y Secado)</t>
         </is>
       </c>
       <c r="I59" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -3635,7 +3641,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>PLANIFICADOR DE MANTENIMIENTO</t>
+          <t>JEFE DE PROYECTOS</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
@@ -3643,7 +3649,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>4808 MAINTENANCE MNG STAFF</t>
+          <t>4600 PROYECTOS</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -3651,23 +3657,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F60" s="13" t="inlineStr">
+      <c r="F60" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-PY-D1</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>Planificador de mantenimiento</t>
+          <t>Jefe de Proyectos</t>
         </is>
       </c>
       <c r="I60" s="9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J60" s="5" t="inlineStr"/>
     </row>
@@ -3679,7 +3685,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>PROGRAMADOR DE PRODUCCCION</t>
+          <t>PLANIFICADOR DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
@@ -3687,7 +3693,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>4300 PLANTABAL SCH</t>
+          <t>4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -3695,23 +3701,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr">
+      <c r="F61" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1</t>
+          <t>GE-SO-MA-D1</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Programador de Producción</t>
+          <t>Planificador de mantenimiento</t>
         </is>
       </c>
       <c r="I61" s="6" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J61" s="4" t="inlineStr"/>
     </row>
@@ -3723,15 +3729,15 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE MANTENIMIENTO</t>
+          <t>PROGRAMADOR DE PRODUCCCION</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>4808 MAINTENANCE MNG STAFF</t>
+          <t>4300 PLANTABAL SCH</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -3739,23 +3745,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F62" s="13" t="inlineStr">
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-MA-D1</t>
+          <t>GE-SO-PO-D1</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>Supervisor de mantenimiento</t>
+          <t>Programador de Producción</t>
         </is>
       </c>
       <c r="I62" s="9" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="J62" s="5" t="inlineStr"/>
     </row>
@@ -3767,15 +3773,15 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE PRODUCCIÓN</t>
+          <t>SUPERVISOR DE MANTENIMIENTO</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>3010 KITS PRODUCTION - PGS / 3821 SUP DE PRODUCCION</t>
+          <t>4808 MAINTENANCE MNG STAFF</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3783,21 +3789,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F63" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr"/>
-      <c r="H63" s="4" t="inlineStr"/>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>GE-SO-MA-D1</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Supervisor de mantenimiento</t>
+        </is>
+      </c>
       <c r="I63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -3807,15 +3817,15 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>TECNICO DE INVENTARIO</t>
+          <t>SUPERVISOR DE PRODUCCIÓN</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>4950 INVENTARY</t>
+          <t>3010 KITS PRODUCTION - PGS / 3821 SUP DE PRODUCCION</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -3823,43 +3833,39 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F64" s="13" t="inlineStr">
-        <is>
-          <t>ANALIZADO</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>GE-SO-CI-D1</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>Técnico de Inventario</t>
-        </is>
-      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>SIN ANALIZAR</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="J64" s="5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Requiere elaboración de matriz IPERC</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>QSE &amp; Operational Excellence</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>ANALISTA DE CALIDAD</t>
+          <t>TECNICO DE INVENTARIO</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>4500 PLANTABAL QUALITY</t>
+          <t>4950 INVENTARY</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3867,23 +3873,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F65" s="12" t="inlineStr">
+      <c r="F65" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-CC-D1</t>
+          <t>GE-SO-CI-D1</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Analista de calidad</t>
+          <t>Técnico de Inventario</t>
         </is>
       </c>
       <c r="I65" s="6" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="J65" s="4" t="inlineStr"/>
     </row>
@@ -3895,11 +3901,11 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>COORDINADOR DE CALIDAD</t>
+          <t>ANALISTA DE CALIDAD</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
@@ -3911,7 +3917,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F66" s="13" t="inlineStr">
+      <c r="F66" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -3923,7 +3929,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>Coordinador de calidad</t>
+          <t>Analista de calidad</t>
         </is>
       </c>
       <c r="I66" s="9" t="n">
@@ -3939,15 +3945,15 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>COORDINADOR DE EXCELENCIA OPERACIONAL</t>
+          <t>COORDINADOR DE CALIDAD</t>
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>4650 EXCELENCIA OPERACIONAL</t>
+          <t>4500 PLANTABAL QUALITY</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3955,23 +3961,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F67" s="12" t="inlineStr">
+      <c r="F67" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-EO-D1</t>
+          <t>GE-SO-CC-D1</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Coordinador de Excelencia Operacional</t>
+          <t>Coordinador de calidad</t>
         </is>
       </c>
       <c r="I67" s="6" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="J67" s="4" t="inlineStr"/>
     </row>
@@ -3983,15 +3989,15 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>COORDINADORA DE CERTIFICACIONES</t>
+          <t>COORDINADOR DE EXCELENCIA OPERACIONAL</t>
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>4350 CERTIFICACION FSC</t>
+          <t>4650 EXCELENCIA OPERACIONAL</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -3999,23 +4005,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F68" s="13" t="inlineStr">
+      <c r="F68" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-CE-D1</t>
+          <t>GE-SO-EO-D1</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>Coordinador/a de Certificaciones</t>
+          <t>Coordinador de Excelencia Operacional</t>
         </is>
       </c>
       <c r="I68" s="9" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J68" s="5" t="inlineStr"/>
     </row>
@@ -4027,7 +4033,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>ESPECIALISTA DE CERTIFICACIONES</t>
+          <t>COORDINADORA DE CERTIFICACIONES</t>
         </is>
       </c>
       <c r="C69" s="6" t="n">
@@ -4043,7 +4049,7 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F69" s="12" t="inlineStr">
+      <c r="F69" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
@@ -4055,11 +4061,11 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Especialista de Certificaciones</t>
+          <t>Coordinador/a de Certificaciones</t>
         </is>
       </c>
       <c r="I69" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J69" s="4" t="inlineStr"/>
     </row>
@@ -4071,7 +4077,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>GERENTE DE CALIDAD Y CERTIFICACIONES</t>
+          <t>ESPECIALISTA DE CERTIFICACIONES</t>
         </is>
       </c>
       <c r="C70" s="9" t="n">
@@ -4079,7 +4085,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>4500 PLANTABAL QUALITY</t>
+          <t>4350 CERTIFICACION FSC</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -4087,29 +4093,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F70" s="13" t="inlineStr">
+      <c r="F70" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-CC-D1</t>
+          <t>GE-SO-CE-D1</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>QSE &amp; Operational Excellence Manager</t>
+          <t>Especialista de Certificaciones</t>
         </is>
       </c>
       <c r="I70" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="J70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -4119,15 +4121,15 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>INGENIERO DE SEGURIDAD  Y AMBIENTE</t>
+          <t>GERENTE DE CALIDAD Y CERTIFICACIONES</t>
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>4203 SEGURIDAD OCUPACIONAL Y AMBIENTE</t>
+          <t>4500 PLANTABAL QUALITY</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -4135,25 +4137,29 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F71" s="12" t="inlineStr">
+      <c r="F71" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-EHS-D1</t>
+          <t>GE-SO-CC-D1</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Ingeniero de seguridad y ambiente</t>
+          <t>QSE &amp; Operational Excellence Manager</t>
         </is>
       </c>
       <c r="I71" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>Denominación distinta entre matriz y head count (equivalencia validada)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -4163,15 +4169,15 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>TECNICO DE CALIDAD</t>
+          <t>INGENIERO DE SEGURIDAD  Y AMBIENTE</t>
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>4500 PLANTABAL QUALITY</t>
+          <t>4203 SEGURIDAD OCUPACIONAL Y AMBIENTE</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -4179,23 +4185,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F72" s="13" t="inlineStr">
+      <c r="F72" s="12" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-CC-D1</t>
+          <t>GE-SO-EHS-D1</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>Técnico de calidad</t>
+          <t>Ingeniero de seguridad y ambiente</t>
         </is>
       </c>
       <c r="I72" s="9" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="J72" s="5" t="inlineStr"/>
     </row>
@@ -4207,15 +4213,15 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>TECNICO DE CERTIFICACIONES</t>
+          <t>TECNICO DE CALIDAD</t>
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>4350 CERTIFICACION FSC</t>
+          <t>4500 PLANTABAL QUALITY / 4507 QUALITY SD</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -4223,23 +4229,23 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F73" s="12" t="inlineStr">
+      <c r="F73" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-CE-D1</t>
+          <t>GE-SO-CC-D1</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Técnico de Certificaciones</t>
+          <t>Técnico de calidad</t>
         </is>
       </c>
       <c r="I73" s="6" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="J73" s="4" t="inlineStr"/>
     </row>
@@ -4251,44 +4257,88 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
+          <t>TECNICO DE CERTIFICACIONES</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>4350 CERTIFICACION FSC</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Quevedo</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-CE-D1</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Técnico de Certificaciones</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="J74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>QSE &amp; Operational Excellence</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
           <t>TECNICO DE SEGURIDAD Y AMBIENTE</t>
         </is>
       </c>
-      <c r="C74" s="9" t="n">
+      <c r="C75" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>4203 SEGURIDAD OCUPACIONAL Y AMBIENTE</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F74" s="13" t="inlineStr">
+      <c r="F75" s="13" t="inlineStr">
         <is>
           <t>ANALIZADO</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>GE-SO-EHS-D1</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>Tecnico de seguridad y ambiente</t>
         </is>
       </c>
-      <c r="I74" s="9" t="n">
+      <c r="I75" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="J74" s="5" t="inlineStr"/>
+      <c r="J75" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J74"/>
+  <autoFilter ref="A4:J75"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -4303,7 +4353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4407,12 +4457,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>CHOFER</t>
+          <t>COORDINADOR DE SEGURIDAD FISICA</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
@@ -4420,12 +4470,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
+          <t>1200 PLANTATION MANAGEMENT</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -4444,7 +4494,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>GERENTE GENERAL</t>
+          <t>CHOFER</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -4452,7 +4502,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -4471,12 +4521,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>GERENTE GENERAL</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
@@ -4484,12 +4534,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>5930 3ACM Expenses</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -4503,12 +4553,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>ANALISTA DE IMPUESTOS</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
@@ -4521,7 +4571,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5930 3ACM Expenses</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -4540,7 +4590,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>ANALISTA DE REDES</t>
+          <t>ANALISTA DE IMPUESTOS</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -4553,7 +4603,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -4700,7 +4750,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>MENSAJERO / REPARTIDOR</t>
+          <t>SENIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
@@ -4713,7 +4763,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -4727,12 +4777,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>SENIOR BUSINESS CONTROLLER</t>
+          <t>APRENDIZ</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -4740,12 +4790,12 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
+          <t>3801 PLANTABAL MANTENANCE #1</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -4764,7 +4814,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>APRENDIZ</t>
+          <t>JEFE DE BODEGA</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
@@ -4777,7 +4827,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>3801 PLANTABAL MANTENANCE #1</t>
+          <t>2500 SERVICE CENTER</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -4788,40 +4838,8 @@
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Operaciones</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>JEFE DE BODEGA</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>2500 SERVICE CENTER</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Elaborar matriz IPERC para el puesto</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:H18"/>
+  <autoFilter ref="A4:H17"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
@@ -4836,7 +4854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5309,112 +5327,149 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-FI-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
+          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>(no consta)</t>
+          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Cargo nuevo no registrado</t>
+          <t>Regularizado - cerrado</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>ANALIZADO en matriz / NO CONSTA en head count V1.1</t>
+          <t>REGULARIZADO - consta en el head count de octubre 2026 con la denominacion de la matriz</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Incorporar el cargo a la base de head count</t>
+          <t>Ninguna. Accion correctiva cumplida.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-FI-D1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>PEOPLE OPERATIONS PARTNER</t>
+          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>(no consta)</t>
+          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Cargo nuevo no registrado</t>
+          <t>Regularizado - cerrado</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>ANALIZADO en matriz / NO CONSTA en head count V1.1</t>
+          <t>REGULARIZADO - consta en el head count de octubre 2026</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Incorporar el cargo a la base de head count</t>
+          <t>Ninguna. Accion correctiva cumplida.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>GE-SO-TH-D1</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>PEOPLE OPERATIONS PARTNER</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>PEOPLE OPERATIONS PARTNER</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Regularizado - cerrado</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>REGULARIZADO - consta en el head count de octubre 2026</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Ninguna. Accion correctiva cumplida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>GE-SO-FI-D1</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>COORDINADOR DE TESORERIA</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>(no existe)</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Cargo obsoleto</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>CARGO INEXISTENTE - suprimido de la estructura</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>ELIMINAR el bloque completo de la matriz GE-SO-FI-D1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G18"/>
+  <autoFilter ref="A4:G19"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -5986,4 +6041,409 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CAMBIOS RESPECTO AL CORTE ANTERIOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tipo de cambio</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Área</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>N° personas</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Estado de cobertura</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Acción sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ALTA - cargo nuevo</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verificar cobertura</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ALTA - cargo nuevo</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>COORDINADOR DE SEGURIDAD FISICA</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verificar cobertura</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ALTA - cargo nuevo</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>MEDICO</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verificar cobertura</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ALTA - cargo nuevo</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>PEOPLE OPERATIONS PARTNER</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verificar cobertura</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>VARIACIÓN de dotación (2 → 1)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>IT&amp;FIN</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>COORDINADOR CONTABLE</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Sin acción si el cargo ya está cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ALTA - cargo nuevo</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>IT&amp;FIN</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Verificar cobertura</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>VARIACIÓN de dotación (3 → 2)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Operaciones</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>TECNICO DE INVENTARIO</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Sin acción si el cargo ya está cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>VARIACIÓN de dotación (4 → 3)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>QSE &amp; Operational Excellence</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>TECNICO DE CALIDAD</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Sin acción si el cargo ya está cubierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>BAJA - cargo ya no consta</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>AUXILIAR ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>BAJA - cargo ya no consta</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>ADM-L&amp;RH</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>MÉDICO OCUPACIONAL</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BAJA - cargo ya no consta</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>IT&amp;FIN</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>ANALISTA DE REDES</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>BAJA - cargo ya no consta</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>IT&amp;FIN</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>MENSAJERO / REPARTIDOR</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F16"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Cobertura_IPERC_Administrativos_CAR.xlsx
+++ b/Cobertura_IPERC_Administrativos_CAR.xlsx
@@ -13,16 +13,14 @@
     <sheet name="4. Brechas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5. Observaciones" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="6. Trazabilidad" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7. Cambios del mes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Alcance y criterios'!$A$4:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Resumen por área'!$A$4:$I$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Matriz consolidada'!$A$4:$J$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Brechas'!$A$4:$H$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. Observaciones'!$A$4:$G$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Trazabilidad'!$A$4:$F$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'7. Cambios del mes'!$A$4:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Trazabilidad'!$A$4:$F$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -566,7 +564,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 22/10/2026</t>
         </is>
       </c>
     </row>
@@ -780,7 +778,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 22/10/2026</t>
         </is>
       </c>
     </row>
@@ -867,29 +865,29 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Operaciones</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -900,26 +898,26 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>2</v>
@@ -1105,22 +1103,22 @@
         <v>71</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F13" s="15" t="n">
         <v>99</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I13" s="14" t="inlineStr"/>
     </row>
@@ -1165,7 +1163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 22/10/2026</t>
         </is>
       </c>
     </row>
@@ -3833,21 +3831,25 @@
           <t>Quevedo</t>
         </is>
       </c>
-      <c r="F64" s="17" t="inlineStr">
-        <is>
-          <t>SIN ANALIZAR</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr"/>
-      <c r="H64" s="5" t="inlineStr"/>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>ANALIZADO</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>GE-SO-PD-D2</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Supervisor de producción</t>
+        </is>
+      </c>
       <c r="I64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>Requiere elaboración de matriz IPERC</t>
-        </is>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -4353,7 +4355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4376,7 +4378,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 22/10/2026</t>
         </is>
       </c>
     </row>
@@ -4425,16 +4427,16 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Operaciones</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE PRODUCCIÓN</t>
+          <t>COORDINADOR DE SEGURIDAD FISICA</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -4443,7 +4445,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>3010 KITS PRODUCTION - PGS / 3821 SUP DE PRODUCCION</t>
+          <t>1200 PLANTATION MANAGEMENT</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -4457,12 +4459,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>COORDINADOR DE SEGURIDAD FISICA</t>
+          <t>CHOFER</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
@@ -4470,12 +4472,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1200 PLANTATION MANAGEMENT</t>
+          <t>5800 GENERAL MANAGEMENT</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -4494,7 +4496,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>CHOFER</t>
+          <t>GERENTE GENERAL</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -4502,7 +4504,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -4521,12 +4523,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>GERENTE GENERAL</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
@@ -4534,12 +4536,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Quevedo</t>
+          <t>Samborondon</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>5800 GENERAL MANAGEMENT</t>
+          <t>5930 3ACM Expenses</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -4553,12 +4555,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>ANALISTA DE IMPUESTOS</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
@@ -4571,7 +4573,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>5930 3ACM Expenses</t>
+          <t>5300 FINANCE</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -4590,7 +4592,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>ANALISTA DE IMPUESTOS</t>
+          <t>DIRECTOR FINANCIERO</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -4622,7 +4624,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>DIRECTOR FINANCIERO</t>
+          <t>GERENTE FINANCIERO</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
@@ -4654,7 +4656,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>GERENTE FINANCIERO</t>
+          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
@@ -4667,7 +4669,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>5300 FINANCE</t>
+          <t>5400 IT</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -4686,7 +4688,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
@@ -4699,7 +4701,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>5400 IT</t>
+          <t>5934 BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -4718,7 +4720,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>SENIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
@@ -4745,12 +4747,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>SENIOR BUSINESS CONTROLLER</t>
+          <t>APRENDIZ</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
@@ -4758,12 +4760,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Samborondon</t>
+          <t>Quevedo</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>5934 BUSINESS CONTROLLER</t>
+          <t>3801 PLANTABAL MANTENANCE #1</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -4782,7 +4784,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>APRENDIZ</t>
+          <t>JEFE DE BODEGA</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -4795,7 +4797,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>3801 PLANTABAL MANTENANCE #1</t>
+          <t>2500 SERVICE CENTER</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -4806,40 +4808,8 @@
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Operaciones</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>JEFE DE BODEGA</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Quevedo</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>2500 SERVICE CENTER</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Elaborar matriz IPERC para el puesto</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:H17"/>
+  <autoFilter ref="A4:H16"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
@@ -4876,7 +4846,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 22/10/2026</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5505,7 +5475,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
+          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 22/10/2026</t>
         </is>
       </c>
     </row>
@@ -5824,622 +5794,245 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PGS-D1</t>
+          <t>GE-SO-PD-D2</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Engicore</t>
+          <t>Supervisor de producción</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Diseño e Ingenieria (9) · Ingeniero de Diseño e Ingenieria (14) · Analista de Diseño e Ingenieria (9)</t>
+          <t>Supervisor de producción (76)</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>f4a8175b-GE-SO-PGS-D1_-_Engicore.xlsx</t>
+          <t>92b21579-GE-SO-PD-D2_-_Supervisores_de_Producci_n.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-PO-D1</t>
+          <t>GE-SO-PGS-D1</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Planificación y Logística</t>
+          <t>Engicore</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Jefe de Planificación y Logística (11) · Coordinador de Supply Chain (6) · Programador de Producción (8) · Analista de Supply Chain (6)</t>
+          <t>Jefe de Diseño e Ingenieria (9) · Ingeniero de Diseño e Ingenieria (14) · Analista de Diseño e Ingenieria (9)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1fa9982d-GE-SO-PO-D1_-_Planificaci_n_y_Log_stica.xlsx</t>
+          <t>f4a8175b-GE-SO-PGS-D1_-_Engicore.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-PY-D1</t>
+          <t>GE-SO-PO-D1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Proyectos</t>
+          <t>Planificación y Logística</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Jefe de Proyectos (20) · Ingeniero de Proyectos (15) · Analista de Proyectos (16)</t>
+          <t>Jefe de Planificación y Logística (11) · Coordinador de Supply Chain (6) · Programador de Producción (8) · Analista de Supply Chain (6)</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>933cde5a-GE-SO-PY-D1_-_Proyectos.xlsx</t>
+          <t>1fa9982d-GE-SO-PO-D1_-_Planificaci_n_y_Log_stica.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-RL-D35</t>
+          <t>GE-SO-PY-D1</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Operations Mng Staff</t>
+          <t>Proyectos</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Director de Operaciones (14) · Gerente de Producción (16) · Jefe de Producción (MV y Secado) (18) · Auxiliar Administrativo (12)</t>
+          <t>Jefe de Proyectos (20) · Ingeniero de Proyectos (15) · Analista de Proyectos (16)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>fe6c6893-Matriz_IPERC_Plantabal_Operations_Mng_Staff.xlsx</t>
+          <t>933cde5a-GE-SO-PY-D1_-_Proyectos.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-SC-D1</t>
+          <t>GE-SO-RL-D35</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Compras</t>
+          <t>Operations Mng Staff</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Analista Supply Chain (13) · Analista Compras (14) · Jefe de Compras (13)</t>
+          <t>Director de Operaciones (14) · Gerente de Producción (16) · Jefe de Producción (MV y Secado) (18) · Auxiliar Administrativo (12)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>9c752964-GE-SO-SC-D1_-_Compras.xlsx</t>
+          <t>fe6c6893-Matriz_IPERC_Plantabal_Operations_Mng_Staff.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>GE-SO-SF-D1</t>
+          <t>GE-SO-SC-D1</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Salud Ocupacional</t>
+          <t>Compras</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
         <v>3</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Medico Ocupacional (18) · Enfermero Ocupacional (10) · Auxiliar de servicios de salud (11)</t>
+          <t>Analista Supply Chain (13) · Analista Compras (14) · Jefe de Compras (13)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>cf092d8f-GE-SO-SF-D1_-_Salud_ocupacional.xlsx</t>
+          <t>9c752964-GE-SO-SC-D1_-_Compras.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>GE-SO-TH-D1</t>
+          <t>GE-SO-SF-D1</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>RECURSOS HUMANOS</t>
+          <t>Salud Ocupacional</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>339</v>
+        <v>39</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>HR DIRECTOR AMERICAS (36) · HR BUSINNES PARTNER AMERICAS (42) · BUSINNES PARTNER DE RECURSOS HUMANOS (28) · COORDINADORA DE DESARROLLO ORGANIZACIONAL (49) · PEOPLE OPERATIONS PARTNER (42) · ANALISTA DE RECURSOS HUMANOS (72) · ANALISTA DE RECURSOS HUMANOS Y NÓMINA (28) · ANALISTA DE DESARROLLO ORGANIZACIONAL (42)</t>
+          <t>Medico Ocupacional (18) · Enfermero Ocupacional (10) · Auxiliar de servicios de salud (11)</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>b206b7b5-GE-SO-TH-D1_-_RRHH.xlsx</t>
+          <t>cf092d8f-GE-SO-SF-D1_-_Salud_ocupacional.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>GE-SO-TH-D1</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>RECURSOS HUMANOS</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>339</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>HR DIRECTOR AMERICAS (36) · HR BUSINNES PARTNER AMERICAS (42) · BUSINNES PARTNER DE RECURSOS HUMANOS (28) · COORDINADORA DE DESARROLLO ORGANIZACIONAL (49) · PEOPLE OPERATIONS PARTNER (42) · ANALISTA DE RECURSOS HUMANOS (72) · ANALISTA DE RECURSOS HUMANOS Y NÓMINA (28) · ANALISTA DE DESARROLLO ORGANIZACIONAL (42)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>b206b7b5-GE-SO-TH-D1_-_RRHH.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>1179</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>1255</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F22"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CAMBIOS RESPECTO AL CORTE ANTERIOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>PLANTACIONES DE BALSA PLANTABAL S.A. / 3A CORE MATERIALS  ·  Control de cobertura IPERC - Personal administrativo  ·  Corte 14/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tipo de cambio</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Área</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Cargo</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>N° personas</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Estado de cobertura</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Acción sugerida</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>ALTA - cargo nuevo</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ADM-L&amp;RH</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>AUXILIAR DE SERVICIOS DE SALUD</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verificar cobertura</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>ALTA - cargo nuevo</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>ADM-L&amp;RH</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>COORDINADOR DE SEGURIDAD FISICA</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Verificar cobertura</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>ALTA - cargo nuevo</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>ADM-L&amp;RH</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>MEDICO</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verificar cobertura</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>ALTA - cargo nuevo</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>ADM-L&amp;RH</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>PEOPLE OPERATIONS PARTNER</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Verificar cobertura</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>VARIACIÓN de dotación (2 → 1)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>IT&amp;FIN</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>COORDINADOR CONTABLE</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Sin acción si el cargo ya está cubierto</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>ALTA - cargo nuevo</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>IT&amp;FIN</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>JEFE DE CONTABILIDAD E IMPUESTOS</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Verificar cobertura</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Confirmar si existe matriz IPERC que cubra el puesto</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>VARIACIÓN de dotación (3 → 2)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Operaciones</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>TECNICO DE INVENTARIO</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Sin acción si el cargo ya está cubierto</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>VARIACIÓN de dotación (4 → 3)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>QSE &amp; Operational Excellence</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>TECNICO DE CALIDAD</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Sin acción si el cargo ya está cubierto</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>BAJA - cargo ya no consta</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>ADM-L&amp;RH</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>AUXILIAR ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>BAJA - cargo ya no consta</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>ADM-L&amp;RH</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>MÉDICO OCUPACIONAL</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>BAJA - cargo ya no consta</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>IT&amp;FIN</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>ANALISTA DE REDES</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>BAJA - cargo ya no consta</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>IT&amp;FIN</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>MENSAJERO / REPARTIDOR</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Evaluar si corresponde retirar el bloque de la matriz IPERC</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:F16"/>
+  <autoFilter ref="A4:F23"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
